--- a/Data/FlightPlan/FPL_19OCT26.xlsx
+++ b/Data/FlightPlan/FPL_19OCT26.xlsx
@@ -143,6 +143,9 @@
     <t>11:10</t>
   </si>
   <si>
+    <t>11:24</t>
+  </si>
+  <si>
     <t>13:00</t>
   </si>
   <si>
@@ -245,6 +248,9 @@
     <t>07:30</t>
   </si>
   <si>
+    <t>07:28</t>
+  </si>
+  <si>
     <t>09:00</t>
   </si>
   <si>
@@ -356,6 +362,9 @@
     <t>08:15</t>
   </si>
   <si>
+    <t>08:07</t>
+  </si>
+  <si>
     <t>08:45</t>
   </si>
   <si>
@@ -404,6 +413,9 @@
     <t>08:55</t>
   </si>
   <si>
+    <t>09:10</t>
+  </si>
+  <si>
     <t>13:10</t>
   </si>
   <si>
@@ -449,6 +461,9 @@
     <t>08:20</t>
   </si>
   <si>
+    <t>08:18</t>
+  </si>
+  <si>
     <t>08:50</t>
   </si>
   <si>
@@ -596,6 +611,9 @@
     <t>VN-A553</t>
   </si>
   <si>
+    <t>07:53</t>
+  </si>
+  <si>
     <t>THD</t>
   </si>
   <si>
@@ -749,6 +767,9 @@
     <t>VN-A632</t>
   </si>
   <si>
+    <t>08:01</t>
+  </si>
+  <si>
     <t>09:55</t>
   </si>
   <si>
@@ -830,6 +851,9 @@
     <t>07:40</t>
   </si>
   <si>
+    <t>07:32</t>
+  </si>
+  <si>
     <t>12:35</t>
   </si>
   <si>
@@ -845,6 +869,9 @@
     <t>VN-A642</t>
   </si>
   <si>
+    <t>08:57</t>
+  </si>
+  <si>
     <t>20:35</t>
   </si>
   <si>
@@ -875,6 +902,9 @@
     <t>09:05</t>
   </si>
   <si>
+    <t>08:44</t>
+  </si>
+  <si>
     <t>SAI</t>
   </si>
   <si>
@@ -893,6 +923,9 @@
     <t>VN-A647</t>
   </si>
   <si>
+    <t>12:02</t>
+  </si>
+  <si>
     <t>17:00</t>
   </si>
   <si>
@@ -926,12 +959,18 @@
     <t>05:40</t>
   </si>
   <si>
+    <t>07:22</t>
+  </si>
+  <si>
     <t>16:05</t>
   </si>
   <si>
     <t>VN-A653</t>
   </si>
   <si>
+    <t>14:13</t>
+  </si>
+  <si>
     <t>HND</t>
   </si>
   <si>
@@ -965,9 +1004,6 @@
     <t>VN-A658</t>
   </si>
   <si>
-    <t>09:10</t>
-  </si>
-  <si>
     <t>22:45</t>
   </si>
   <si>
@@ -1031,6 +1067,9 @@
     <t>VN-A672</t>
   </si>
   <si>
+    <t>08:28</t>
+  </si>
+  <si>
     <t>01:15</t>
   </si>
   <si>
@@ -1049,6 +1088,9 @@
     <t>07:35</t>
   </si>
   <si>
+    <t>07:42</t>
+  </si>
+  <si>
     <t>08:05</t>
   </si>
   <si>
@@ -1118,9 +1160,15 @@
     <t>VN-A698</t>
   </si>
   <si>
+    <t>08:56</t>
+  </si>
+  <si>
     <t>VN-A810</t>
   </si>
   <si>
+    <t>06:33</t>
+  </si>
+  <si>
     <t>UFA</t>
   </si>
   <si>
@@ -1163,7 +1211,7 @@
     <t>Total Record(s): 334</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 19, 2026 05:30</t>
+    <t xml:space="preserve">Generated on  Oct 19, 2026 07:32</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2037,7 +2085,9 @@
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
+      <c t="s" r="M17" s="7">
+        <v>44</v>
+      </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c t="s" r="A18" s="6">
@@ -2063,10 +2113,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I18" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="J18" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
@@ -2093,13 +2143,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H19" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="I19" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c t="s" r="J19" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -2132,7 +2182,7 @@
       </c>
       <c r="D21" s="7"/>
       <c t="s" r="E21" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F21" s="7">
         <v>321</v>
@@ -2141,13 +2191,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H21" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I21" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J21" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -2165,22 +2215,22 @@
       </c>
       <c r="D22" s="7"/>
       <c t="s" r="E22" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F22" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G22" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H22" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I22" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c t="s" r="J22" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
@@ -2198,7 +2248,7 @@
       </c>
       <c r="D23" s="7"/>
       <c t="s" r="E23" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" s="7">
         <v>321</v>
@@ -2210,10 +2260,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I23" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c t="s" r="J23" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -2246,22 +2296,22 @@
       </c>
       <c r="D25" s="7"/>
       <c t="s" r="E25" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F25" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G25" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="H25" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I25" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J25" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2279,7 +2329,7 @@
       </c>
       <c r="D26" s="7"/>
       <c t="s" r="E26" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F26" s="7">
         <v>321</v>
@@ -2291,10 +2341,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2312,7 +2362,7 @@
       </c>
       <c r="D27" s="7"/>
       <c t="s" r="E27" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F27" s="7">
         <v>321</v>
@@ -2324,10 +2374,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I27" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2345,7 +2395,7 @@
       </c>
       <c r="D28" s="7"/>
       <c t="s" r="E28" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F28" s="7">
         <v>321</v>
@@ -2357,10 +2407,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -2378,7 +2428,7 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
@@ -2390,10 +2440,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -2426,7 +2476,7 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
@@ -2435,13 +2485,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H31" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2459,19 +2509,19 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G32" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H32" s="8">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J32" s="7">
         <v>23</v>
@@ -2492,22 +2542,22 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G33" s="8">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="H33" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2540,7 +2590,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2549,17 +2599,19 @@
         <v>29</v>
       </c>
       <c t="s" r="H35" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
+      <c t="s" r="M35" s="7">
+        <v>79</v>
+      </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c t="s" r="A36" s="6">
@@ -2573,13 +2625,13 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G36" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="H36" s="8">
         <v>29</v>
@@ -2588,7 +2640,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2606,7 +2658,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -2615,13 +2667,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2639,22 +2691,22 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G38" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="H38" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2672,7 +2724,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -2681,13 +2733,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H39" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2705,22 +2757,22 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G40" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H40" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2738,7 +2790,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -2747,13 +2799,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H41" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I41" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2771,22 +2823,22 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H42" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2819,13 +2871,13 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>29</v>
@@ -2834,7 +2886,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2852,7 +2904,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -2867,7 +2919,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -2885,7 +2937,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -2894,13 +2946,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2933,7 +2985,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -2942,13 +2994,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -2966,19 +3018,19 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="J49" s="7">
         <v>32</v>
@@ -2999,7 +3051,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3008,13 +3060,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3032,22 +3084,22 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
+        <v>99</v>
+      </c>
+      <c r="F51" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G51" s="8">
+        <v>100</v>
+      </c>
+      <c t="s" r="H51" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I51" s="7">
         <v>97</v>
       </c>
-      <c r="F51" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G51" s="8">
-        <v>98</v>
-      </c>
-      <c t="s" r="H51" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I51" s="7">
-        <v>95</v>
-      </c>
       <c t="s" r="J51" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3080,22 +3132,22 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3113,7 +3165,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3122,13 +3174,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3146,22 +3198,22 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3194,7 +3246,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3206,14 +3258,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
-      <c r="M57" s="7"/>
+      <c t="s" r="M57" s="7">
+        <v>117</v>
+      </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c t="s" r="A58" s="6">
@@ -3227,7 +3281,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3239,10 +3293,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3260,7 +3314,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3275,7 +3329,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3293,7 +3347,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3305,10 +3359,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3326,7 +3380,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3338,7 +3392,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c t="s" r="J61" s="7">
         <v>24</v>
@@ -3359,7 +3413,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3371,7 +3425,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c t="s" r="J62" s="7">
         <v>37</v>
@@ -3407,7 +3461,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3416,13 +3470,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3440,22 +3494,22 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3473,7 +3527,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3482,13 +3536,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3506,22 +3560,22 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3554,7 +3608,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3563,17 +3617,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
-      <c r="M69" s="7"/>
+      <c t="s" r="M69" s="7">
+        <v>134</v>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c t="s" r="A70" s="6">
@@ -3587,13 +3643,13 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>17</v>
@@ -3602,7 +3658,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3620,7 +3676,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3629,13 +3685,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3653,22 +3709,22 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H72" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3686,7 +3742,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3695,13 +3751,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3719,19 +3775,19 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c t="s" r="J74" s="7">
         <v>24</v>
@@ -3767,7 +3823,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3779,10 +3835,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3800,7 +3856,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3809,13 +3865,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3833,22 +3889,22 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3881,7 +3937,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -3890,17 +3946,19 @@
         <v>29</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
+      <c t="s" r="M80" s="7">
+        <v>56</v>
+      </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c t="s" r="A81" s="6">
@@ -3914,26 +3972,28 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
-      <c r="M81" s="7"/>
+      <c t="s" r="M81" s="7">
+        <v>150</v>
+      </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c t="s" r="A82" s="6">
@@ -3947,7 +4007,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -3956,13 +4016,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -3980,22 +4040,22 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4013,7 +4073,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4025,10 +4085,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4046,7 +4106,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4058,10 +4118,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4079,7 +4139,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4091,10 +4151,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4112,7 +4172,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4127,7 +4187,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4160,22 +4220,22 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4193,7 +4253,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4202,13 +4262,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4226,22 +4286,22 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4259,7 +4319,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4268,13 +4328,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4292,22 +4352,22 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4325,7 +4385,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4337,10 +4397,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4358,7 +4418,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4367,13 +4427,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4406,7 +4466,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4415,13 +4475,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4432,36 +4492,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B98" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="C98" s="7">
         <v>14</v>
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c t="s" r="K98" s="7">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -4476,7 +4536,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4488,10 +4548,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4509,7 +4569,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4524,7 +4584,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4542,7 +4602,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4554,7 +4614,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>35</v>
@@ -4575,7 +4635,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4587,10 +4647,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4623,7 +4683,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4635,15 +4695,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -4658,7 +4718,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4670,10 +4730,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4691,7 +4751,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4703,10 +4763,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4724,7 +4784,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4736,10 +4796,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4757,7 +4817,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4766,13 +4826,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4790,13 +4850,13 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
@@ -4805,7 +4865,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4838,7 +4898,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4850,10 +4910,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4871,7 +4931,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4880,13 +4940,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4904,19 +4964,19 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>26</v>
@@ -4937,7 +4997,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -4946,13 +5006,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -4985,7 +5045,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -4994,17 +5054,19 @@
         <v>29</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
+      <c t="s" r="M116" s="7">
+        <v>200</v>
+      </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c t="s" r="A117" s="6">
@@ -5018,19 +5080,19 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>18</v>
@@ -5051,7 +5113,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5060,13 +5122,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5084,22 +5146,22 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5117,7 +5179,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5126,13 +5188,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5150,22 +5212,22 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5194,33 +5256,33 @@
         <v>7615</v>
       </c>
       <c t="s" r="C123" s="7">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c t="s" r="K123" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5231,11 +5293,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C124" s="7">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5244,20 +5306,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c t="s" r="K124" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5272,29 +5334,29 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="K125" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -5309,29 +5371,29 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c t="s" r="K126" s="7">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5346,22 +5408,22 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5394,7 +5456,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5403,13 +5465,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5427,22 +5489,22 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5460,7 +5522,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5469,13 +5531,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I131" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5493,22 +5555,22 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5526,7 +5588,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5535,13 +5597,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5574,7 +5636,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5586,7 +5648,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>18</v>
@@ -5607,7 +5669,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5619,10 +5681,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5640,7 +5702,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5652,10 +5714,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5673,7 +5735,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5682,13 +5744,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5706,19 +5768,19 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>35</v>
@@ -5739,7 +5801,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5751,10 +5813,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5787,7 +5849,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5796,13 +5858,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5820,22 +5882,22 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5853,7 +5915,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5862,13 +5924,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5886,22 +5948,22 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5919,7 +5981,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5928,13 +5990,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5952,22 +6014,22 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6000,7 +6062,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6009,13 +6071,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6033,22 +6095,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6066,22 +6128,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6114,7 +6176,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6126,14 +6188,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
-      <c r="M153" s="7"/>
+      <c t="s" r="M153" s="7">
+        <v>179</v>
+      </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
       <c t="s" r="A154" s="6">
@@ -6147,7 +6211,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6156,20 +6220,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c t="s" r="I154" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="K154" s="7">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6184,22 +6248,22 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6217,7 +6281,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6229,10 +6293,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6250,7 +6314,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6265,7 +6329,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6283,7 +6347,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6292,13 +6356,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6316,22 +6380,22 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6364,27 +6428,27 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -6399,22 +6463,22 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6432,19 +6496,19 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>23</v>
@@ -6465,7 +6529,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6474,13 +6538,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6498,22 +6562,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6546,7 +6610,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6561,11 +6625,13 @@
         <v>38</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
-      <c r="M167" s="7"/>
+      <c t="s" r="M167" s="7">
+        <v>252</v>
+      </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
       <c t="s" r="A168" s="6">
@@ -6579,7 +6645,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6591,10 +6657,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6612,7 +6678,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6624,10 +6690,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6645,7 +6711,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6657,10 +6723,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6678,7 +6744,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6690,10 +6756,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6711,7 +6777,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6720,13 +6786,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6744,22 +6810,22 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6777,7 +6843,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6786,13 +6852,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6810,22 +6876,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6858,7 +6924,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6867,13 +6933,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6891,22 +6957,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6924,7 +6990,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6933,13 +6999,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6957,22 +7023,22 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7005,7 +7071,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7014,13 +7080,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7038,22 +7104,22 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="H183" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7071,7 +7137,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7083,10 +7149,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7104,7 +7170,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7116,10 +7182,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7137,7 +7203,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7146,13 +7212,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7170,22 +7236,22 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7218,7 +7284,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7227,13 +7293,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7251,22 +7317,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7284,22 +7350,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7317,22 +7383,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7350,22 +7416,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7383,22 +7449,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7431,7 +7497,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7440,13 +7506,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7464,13 +7530,13 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>29</v>
@@ -7479,7 +7545,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7497,7 +7563,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7506,13 +7572,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7530,22 +7596,22 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7578,7 +7644,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7590,14 +7656,16 @@
         <v>29</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
-      <c r="M201" s="7"/>
+      <c t="s" r="M201" s="7">
+        <v>280</v>
+      </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
       <c t="s" r="A202" s="6">
@@ -7611,7 +7679,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7620,13 +7688,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c t="s" r="I202" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7644,22 +7712,22 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7677,7 +7745,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7686,13 +7754,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7710,22 +7778,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7758,7 +7826,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7767,13 +7835,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7791,22 +7859,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7824,7 +7892,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7833,13 +7901,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7857,22 +7925,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7905,26 +7973,28 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
-      <c r="M212" s="7"/>
+      <c t="s" r="M212" s="7">
+        <v>286</v>
+      </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
       <c t="s" r="A213" s="6">
@@ -7938,7 +8008,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7947,13 +8017,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -7971,22 +8041,22 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8004,7 +8074,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8013,13 +8083,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8037,22 +8107,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8070,7 +8140,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8079,13 +8149,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8118,7 +8188,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8127,13 +8197,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c t="s" r="I219" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8151,22 +8221,22 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8184,7 +8254,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8193,13 +8263,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8217,22 +8287,22 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8250,7 +8320,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8262,10 +8332,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8283,7 +8353,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8292,13 +8362,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8331,7 +8401,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8343,14 +8413,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
-      <c r="M226" s="7"/>
+      <c t="s" r="M226" s="7">
+        <v>297</v>
+      </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
       <c t="s" r="A227" s="6">
@@ -8364,7 +8436,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8373,13 +8445,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8397,19 +8469,19 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>32</v>
@@ -8430,7 +8502,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8439,13 +8511,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8463,22 +8535,22 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8496,7 +8568,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8505,13 +8577,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8544,22 +8616,22 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8577,7 +8649,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8592,7 +8664,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8625,26 +8697,28 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
-      <c r="M236" s="7"/>
+      <c t="s" r="M236" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
       <c t="s" r="A237" s="6">
@@ -8658,22 +8732,22 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8691,16 +8765,16 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I238" s="7">
         <v>22</v>
@@ -8724,22 +8798,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8772,7 +8846,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8781,13 +8855,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8805,22 +8879,22 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8838,7 +8912,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8850,10 +8924,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8871,7 +8945,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8883,10 +8957,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8904,7 +8978,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -8913,13 +8987,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8937,22 +9011,22 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -8985,22 +9059,22 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9018,7 +9092,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9027,13 +9101,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9051,22 +9125,22 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9084,7 +9158,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9093,13 +9167,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9132,7 +9206,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9141,13 +9215,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9165,22 +9239,22 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9198,7 +9272,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -9207,13 +9281,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9231,22 +9305,22 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9264,7 +9338,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -9279,7 +9353,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9312,7 +9386,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9321,17 +9395,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
-      <c r="M259" s="7"/>
+      <c t="s" r="M259" s="7">
+        <v>316</v>
+      </c>
     </row>
     <row r="260" ht="15" customHeight="1">
       <c t="s" r="A260" s="6">
@@ -9345,22 +9421,22 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9378,7 +9454,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9387,13 +9463,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9411,22 +9487,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9444,7 +9520,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9453,10 +9529,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>33</v>
@@ -9477,22 +9553,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9510,7 +9586,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9522,10 +9598,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9543,7 +9619,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9555,10 +9631,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9591,7 +9667,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9603,14 +9679,16 @@
         <v>29</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
-      <c r="M268" s="7"/>
+      <c t="s" r="M268" s="7">
+        <v>319</v>
+      </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
       <c t="s" r="A269" s="6">
@@ -9624,7 +9702,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9633,13 +9711,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9657,22 +9735,22 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9705,7 +9783,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -9717,10 +9795,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9738,7 +9816,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9750,10 +9828,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9771,7 +9849,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -9783,10 +9861,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9804,7 +9882,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9813,10 +9891,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>18</v>
@@ -9852,7 +9930,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -9861,18 +9939,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>316</v>
+        <v>329</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -9887,26 +9965,28 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
+        <v>229</v>
+      </c>
+      <c t="s" r="H278" s="8">
+        <v>76</v>
+      </c>
+      <c t="s" r="I278" s="7">
         <v>223</v>
       </c>
-      <c t="s" r="H278" s="8">
-        <v>75</v>
-      </c>
-      <c t="s" r="I278" s="7">
-        <v>217</v>
-      </c>
       <c t="s" r="J278" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
-      <c r="M278" s="7"/>
+      <c t="s" r="M278" s="7">
+        <v>118</v>
+      </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
       <c t="s" r="A279" s="6">
@@ -9920,22 +10000,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9953,13 +10033,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>29</v>
@@ -9968,7 +10048,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -9986,7 +10066,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -9995,13 +10075,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10019,22 +10099,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10052,7 +10132,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10061,13 +10141,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10100,7 +10180,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10112,10 +10192,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>318</v>
+        <v>134</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10133,7 +10213,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10145,10 +10225,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10166,7 +10246,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10178,7 +10258,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>32</v>
@@ -10199,7 +10279,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10211,7 +10291,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>23</v>
@@ -10232,7 +10312,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10244,10 +10324,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10280,7 +10360,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10289,13 +10369,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10313,19 +10393,19 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>43</v>
@@ -10346,7 +10426,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10355,13 +10435,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10379,22 +10459,22 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10412,7 +10492,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10421,13 +10501,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10445,22 +10525,22 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10493,7 +10573,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10505,10 +10585,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10526,7 +10606,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10538,10 +10618,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10559,7 +10639,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10571,10 +10651,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10592,7 +10672,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10604,7 +10684,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>23</v>
@@ -10640,7 +10720,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10652,10 +10732,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10673,7 +10753,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10688,7 +10768,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10706,7 +10786,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10715,13 +10795,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10739,22 +10819,22 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10787,7 +10867,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10796,13 +10876,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10820,22 +10900,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10853,7 +10933,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -10862,10 +10942,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>33</v>
@@ -10886,22 +10966,22 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10919,7 +10999,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -10928,13 +11008,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10952,22 +11032,22 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11000,7 +11080,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11012,10 +11092,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11033,7 +11113,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11045,10 +11125,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11066,7 +11146,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11075,13 +11155,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11099,22 +11179,22 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11132,7 +11212,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11141,13 +11221,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11165,22 +11245,22 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11213,27 +11293,27 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11248,7 +11328,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11257,20 +11337,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c t="s" r="K323" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11285,22 +11365,22 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11333,7 +11413,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11345,14 +11425,16 @@
         <v>41</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
-      <c r="M326" s="7"/>
+      <c t="s" r="M326" s="7">
+        <v>352</v>
+      </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
       <c t="s" r="A327" s="6">
@@ -11366,7 +11448,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11378,10 +11460,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>318</v>
+        <v>134</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11399,7 +11481,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11408,13 +11490,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11432,22 +11514,22 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11465,7 +11547,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11474,13 +11556,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11498,22 +11580,22 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11531,7 +11613,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11540,13 +11622,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11564,22 +11646,22 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11612,7 +11694,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11621,17 +11703,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
-      <c r="M335" s="7"/>
+      <c t="s" r="M335" s="7">
+        <v>359</v>
+      </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
       <c t="s" r="A336" s="6">
@@ -11645,22 +11729,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11678,7 +11762,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11687,13 +11771,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11711,22 +11795,22 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11744,7 +11828,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11753,13 +11837,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11777,22 +11861,22 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11810,7 +11894,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -11819,13 +11903,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11843,19 +11927,19 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>36</v>
@@ -11891,22 +11975,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11924,7 +12008,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -11933,13 +12017,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -11957,22 +12041,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12005,27 +12089,27 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>350</v>
+        <v>364</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12040,22 +12124,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12073,7 +12157,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12082,13 +12166,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12106,22 +12190,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12139,7 +12223,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12148,13 +12232,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12172,22 +12256,22 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12220,7 +12304,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12229,13 +12313,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12253,22 +12337,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12286,7 +12370,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12298,10 +12382,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12334,7 +12418,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12343,13 +12427,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12367,22 +12451,22 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12400,22 +12484,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12448,7 +12532,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12457,17 +12541,19 @@
         <v>29</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
-      <c r="M363" s="7"/>
+      <c t="s" r="M363" s="7">
+        <v>279</v>
+      </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
       <c t="s" r="A364" s="6">
@@ -12481,13 +12567,13 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>29</v>
@@ -12496,7 +12582,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12514,7 +12600,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12523,13 +12609,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12547,22 +12633,22 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12580,22 +12666,22 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12613,22 +12699,22 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12646,7 +12732,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12655,13 +12741,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12694,7 +12780,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12703,18 +12789,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>366</v>
+        <v>380</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -12729,26 +12815,28 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
-      <c r="M372" s="7"/>
+      <c t="s" r="M372" s="7">
+        <v>334</v>
+      </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
       <c t="s" r="A373" s="6">
@@ -12762,7 +12850,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -12774,7 +12862,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>318</v>
+        <v>134</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>31</v>
@@ -12795,7 +12883,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -12807,10 +12895,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12828,7 +12916,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12837,13 +12925,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12861,22 +12949,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12894,7 +12982,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -12903,13 +12991,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12927,22 +13015,22 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12975,7 +13063,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -12987,7 +13075,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>33</v>
@@ -13008,7 +13096,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13020,10 +13108,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13041,7 +13129,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13050,10 +13138,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>27</v>
@@ -13089,7 +13177,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13098,17 +13186,19 @@
         <v>29</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
-      <c r="M384" s="7"/>
+      <c t="s" r="M384" s="7">
+        <v>383</v>
+      </c>
     </row>
     <row r="385" ht="15" customHeight="1">
       <c t="s" r="A385" s="6">
@@ -13122,22 +13212,22 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13155,7 +13245,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13164,13 +13254,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13188,22 +13278,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13221,7 +13311,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13230,13 +13320,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13254,22 +13344,22 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13302,7 +13392,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="F391" s="7">
         <v>330</v>
@@ -13311,18 +13401,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>316</v>
+        <v>385</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -13337,26 +13427,30 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="F392" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c t="s" r="I392" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>211</v>
-      </c>
-      <c r="K392" s="7"/>
+        <v>217</v>
+      </c>
+      <c t="s" r="K392" s="7">
+        <v>80</v>
+      </c>
       <c r="L392" s="7"/>
-      <c r="M392" s="7"/>
+      <c t="s" r="M392" s="7">
+        <v>246</v>
+      </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
       <c t="s" r="A393" s="6">
@@ -13370,22 +13464,22 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13418,22 +13512,22 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="F395" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13466,7 +13560,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
@@ -13475,13 +13569,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13499,22 +13593,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13547,13 +13641,13 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>29</v>
@@ -13562,7 +13656,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13580,7 +13674,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -13589,13 +13683,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13613,22 +13707,22 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13657,26 +13751,26 @@
         <v>5805</v>
       </c>
       <c t="s" r="C404" s="7">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13690,17 +13784,17 @@
         <v>2841</v>
       </c>
       <c t="s" r="C405" s="7">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>41</v>
@@ -13709,7 +13803,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13742,7 +13836,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -13751,7 +13845,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>43</v>
@@ -13775,22 +13869,22 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13798,7 +13892,7 @@
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c t="s" r="A409" s="9">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="B409" s="9"/>
       <c r="C409" s="9"/>
@@ -13818,7 +13912,7 @@
     <row r="410" ht="66" customHeight="1"/>
     <row r="411" ht="16.5" customHeight="1">
       <c t="s" r="A411" s="10">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="B411" s="10"/>
       <c r="C411" s="10"/>
@@ -13831,7 +13925,7 @@
       <c r="J411" s="10"/>
       <c r="K411" s="10"/>
       <c t="s" r="L411" s="11">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="M411" s="11"/>
       <c r="N411" s="11"/>

--- a/Data/FlightPlan/FPL_19OCT26.xlsx
+++ b/Data/FlightPlan/FPL_19OCT26.xlsx
@@ -686,6 +686,9 @@
     <t>VN-A575</t>
   </si>
   <si>
+    <t>09:09</t>
+  </si>
+  <si>
     <t>16:00</t>
   </si>
   <si>
@@ -1118,6 +1121,9 @@
     <t>NGO</t>
   </si>
   <si>
+    <t>13:36</t>
+  </si>
+  <si>
     <t>VN-A683</t>
   </si>
   <si>
@@ -1187,28 +1193,34 @@
     <t>06:33</t>
   </si>
   <si>
+    <t>KZN</t>
+  </si>
+  <si>
+    <t>VN-A811</t>
+  </si>
+  <si>
+    <t>SYD</t>
+  </si>
+  <si>
+    <t>16:36</t>
+  </si>
+  <si>
+    <t>VN-A812</t>
+  </si>
+  <si>
+    <t>BNE</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A815</t>
+  </si>
+  <si>
     <t>OVB</t>
   </si>
   <si>
-    <t>VN-A811</t>
-  </si>
-  <si>
-    <t>SYD</t>
-  </si>
-  <si>
-    <t>16:36</t>
-  </si>
-  <si>
-    <t>VN-A812</t>
-  </si>
-  <si>
-    <t>BNE</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A815</t>
+    <t>VN-A817</t>
   </si>
   <si>
     <t>UFA</t>
@@ -1217,12 +1229,6 @@
     <t>05:15</t>
   </si>
   <si>
-    <t>VN-A817</t>
-  </si>
-  <si>
-    <t>KZN</t>
-  </si>
-  <si>
     <t>VN-A820</t>
   </si>
   <si>
@@ -1232,7 +1238,7 @@
     <t>Total Record(s): 335</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 19, 2026 07:53</t>
+    <t xml:space="preserve">Generated on  Oct 19, 2026 08:00</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5535,7 +5541,9 @@
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
-      <c r="M130" s="7"/>
+      <c t="s" r="M130" s="7">
+        <v>225</v>
+      </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
       <c t="s" r="A131" s="6">
@@ -5660,7 +5668,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>170</v>
@@ -5696,7 +5704,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5708,7 +5716,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>18</v>
@@ -5729,7 +5737,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5744,7 +5752,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5762,7 +5770,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5774,7 +5782,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>157</v>
@@ -5795,7 +5803,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5828,7 +5836,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5840,7 +5848,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>36</v>
@@ -5861,7 +5869,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5876,7 +5884,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5909,7 +5917,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5918,13 +5926,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5942,13 +5950,13 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>30</v>
@@ -5975,7 +5983,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5987,7 +5995,7 @@
         <v>205</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>193</v>
@@ -6008,7 +6016,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6023,7 +6031,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6041,7 +6049,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6050,10 +6058,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>173</v>
@@ -6074,19 +6082,19 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>113</v>
@@ -6122,7 +6130,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6155,7 +6163,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6164,7 +6172,7 @@
         <v>87</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="I151" s="7">
         <v>165</v>
@@ -6188,13 +6196,13 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>87</v>
@@ -6236,7 +6244,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6271,7 +6279,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6280,7 +6288,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>44</v>
@@ -6289,7 +6297,7 @@
         <v>46</v>
       </c>
       <c t="s" r="K155" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
@@ -6308,13 +6316,13 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>17</v>
@@ -6341,7 +6349,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6374,7 +6382,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6407,7 +6415,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6416,7 +6424,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I159" s="7">
         <v>94</v>
@@ -6440,22 +6448,22 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6488,7 +6496,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6500,7 +6508,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>202</v>
@@ -6508,7 +6516,7 @@
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6523,7 +6531,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6532,13 +6540,13 @@
         <v>87</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I163" s="7">
         <v>136</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6556,13 +6564,13 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>30</v>
@@ -6589,7 +6597,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6598,13 +6606,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6622,22 +6630,22 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6670,7 +6678,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6690,7 +6698,7 @@
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -6705,7 +6713,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6720,7 +6728,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6738,7 +6746,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6753,7 +6761,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6771,7 +6779,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6786,7 +6794,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6804,7 +6812,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6816,7 +6824,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>55</v>
@@ -6837,7 +6845,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6870,7 +6878,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6903,7 +6911,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6936,7 +6944,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6948,10 +6956,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6984,7 +6992,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6993,7 +7001,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>199</v>
@@ -7017,13 +7025,13 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>30</v>
@@ -7050,7 +7058,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7062,10 +7070,10 @@
         <v>101</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7083,7 +7091,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7131,7 +7139,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7150,7 +7158,9 @@
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
-      <c r="M183" s="7"/>
+      <c t="s" r="M183" s="7">
+        <v>269</v>
+      </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c t="s" r="A184" s="6">
@@ -7164,7 +7174,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7176,7 +7186,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J184" s="7">
         <v>164</v>
@@ -7197,7 +7207,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7209,10 +7219,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7230,7 +7240,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7263,7 +7273,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7278,7 +7288,7 @@
         <v>159</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7296,7 +7306,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7311,7 +7321,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7344,7 +7354,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7353,7 +7363,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I190" s="7">
         <v>145</v>
@@ -7364,7 +7374,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7379,19 +7389,19 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>87</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>136</v>
@@ -7412,7 +7422,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7445,7 +7455,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7460,7 +7470,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7478,7 +7488,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7487,10 +7497,10 @@
         <v>87</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>210</v>
@@ -7511,19 +7521,19 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>87</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>174</v>
@@ -7559,7 +7569,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7568,10 +7578,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>182</v>
@@ -7592,13 +7602,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>30</v>
@@ -7625,7 +7635,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7634,13 +7644,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>158</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7658,13 +7668,13 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>30</v>
@@ -7706,7 +7716,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7718,15 +7728,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -7741,7 +7751,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7750,13 +7760,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7774,13 +7784,13 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>30</v>
@@ -7807,7 +7817,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7840,7 +7850,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7852,10 +7862,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7888,7 +7898,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7897,7 +7907,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="I208" s="7">
         <v>152</v>
@@ -7921,13 +7931,13 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>30</v>
@@ -7954,7 +7964,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7963,7 +7973,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I210" s="7">
         <v>88</v>
@@ -7987,13 +7997,13 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>30</v>
@@ -8002,7 +8012,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8035,7 +8045,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8055,7 +8065,7 @@
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8070,7 +8080,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8103,7 +8113,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8115,7 +8125,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>47</v>
@@ -8136,7 +8146,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8169,7 +8179,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8184,7 +8194,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8202,7 +8212,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8217,7 +8227,7 @@
         <v>209</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8250,7 +8260,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8259,7 +8269,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>44</v>
@@ -8283,13 +8293,13 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>30</v>
@@ -8316,7 +8326,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8325,13 +8335,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8349,13 +8359,13 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>30</v>
@@ -8364,7 +8374,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8382,7 +8392,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8394,10 +8404,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8415,7 +8425,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8424,10 +8434,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>53</v>
@@ -8463,7 +8473,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8478,12 +8488,12 @@
         <v>57</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -8498,7 +8508,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8531,7 +8541,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8564,7 +8574,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8573,7 +8583,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="I230" s="7">
         <v>208</v>
@@ -8597,13 +8607,13 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>17</v>
@@ -8630,7 +8640,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8642,10 +8652,10 @@
         <v>97</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8678,19 +8688,19 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>167</v>
@@ -8711,7 +8721,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8759,7 +8769,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8779,7 +8789,7 @@
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -8794,7 +8804,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8803,13 +8813,13 @@
         <v>70</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8827,13 +8837,13 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>70</v>
@@ -8860,7 +8870,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8908,7 +8918,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8920,10 +8930,10 @@
         <v>87</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8941,7 +8951,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8974,7 +8984,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8989,7 +8999,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9007,7 +9017,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9040,7 +9050,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9073,7 +9083,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9085,10 +9095,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9121,7 +9131,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9154,7 +9164,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9163,7 +9173,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="I250" s="7">
         <v>125</v>
@@ -9187,13 +9197,13 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>17</v>
@@ -9202,7 +9212,7 @@
         <v>209</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9220,7 +9230,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9232,7 +9242,7 @@
         <v>97</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>53</v>
@@ -9268,7 +9278,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
@@ -9280,7 +9290,7 @@
         <v>192</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>165</v>
@@ -9301,7 +9311,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -9334,7 +9344,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
@@ -9346,7 +9356,7 @@
         <v>168</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>169</v>
@@ -9367,7 +9377,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -9400,7 +9410,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
@@ -9415,7 +9425,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9448,7 +9458,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9460,15 +9470,15 @@
         <v>87</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9483,7 +9493,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9503,7 +9513,7 @@
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -9518,7 +9528,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9533,7 +9543,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9551,7 +9561,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9584,7 +9594,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9617,7 +9627,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9629,7 +9639,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>126</v>
@@ -9650,7 +9660,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9683,7 +9693,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9731,7 +9741,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9751,7 +9761,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -9766,7 +9776,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9775,7 +9785,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="I270" s="7">
         <v>89</v>
@@ -9799,22 +9809,22 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9847,7 +9857,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9880,7 +9890,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -9895,7 +9905,7 @@
         <v>172</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9913,7 +9923,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9925,7 +9935,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>99</v>
@@ -9946,7 +9956,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -9955,10 +9965,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>18</v>
@@ -9994,7 +10004,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10003,18 +10013,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>187</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10029,19 +10039,19 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>77</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>119</v>
@@ -10064,7 +10074,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10073,10 +10083,10 @@
         <v>77</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>180</v>
@@ -10097,13 +10107,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>30</v>
@@ -10130,7 +10140,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10142,7 +10152,7 @@
         <v>101</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>221</v>
@@ -10163,7 +10173,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10178,7 +10188,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10196,7 +10206,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10244,7 +10254,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10256,7 +10266,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>135</v>
@@ -10277,7 +10287,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10310,7 +10320,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10343,7 +10353,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10376,7 +10386,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10388,10 +10398,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10424,7 +10434,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10436,7 +10446,7 @@
         <v>147</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>199</v>
@@ -10457,7 +10467,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10490,7 +10500,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10499,7 +10509,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>22</v>
@@ -10523,13 +10533,13 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>30</v>
@@ -10538,7 +10548,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10556,7 +10566,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -10565,7 +10575,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="I296" s="7">
         <v>75</v>
@@ -10589,22 +10599,22 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10637,7 +10647,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10649,7 +10659,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>164</v>
@@ -10670,7 +10680,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10703,7 +10713,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10715,7 +10725,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>208</v>
@@ -10736,7 +10746,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -10784,7 +10794,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10817,7 +10827,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10850,7 +10860,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -10859,7 +10869,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>156</v>
@@ -10883,13 +10893,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>30</v>
@@ -10931,7 +10941,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -10940,10 +10950,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>215</v>
@@ -10964,19 +10974,19 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>46</v>
@@ -10997,7 +11007,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11030,7 +11040,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11042,10 +11052,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11063,7 +11073,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11072,7 +11082,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>160</v>
@@ -11096,19 +11106,19 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>187</v>
@@ -11144,7 +11154,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11177,7 +11187,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11189,7 +11199,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>182</v>
@@ -11210,7 +11220,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11243,7 +11253,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11258,7 +11268,7 @@
         <v>208</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11276,7 +11286,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11285,13 +11295,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11309,13 +11319,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>17</v>
@@ -11324,7 +11334,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11357,7 +11367,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11369,7 +11379,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>134</v>
@@ -11392,7 +11402,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11404,7 +11414,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>158</v>
@@ -11429,7 +11439,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11444,7 +11454,7 @@
         <v>159</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11477,7 +11487,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11492,12 +11502,12 @@
         <v>78</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -11512,7 +11522,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11527,7 +11537,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11545,7 +11555,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11557,7 +11567,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>72</v>
@@ -11578,7 +11588,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11611,7 +11621,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11644,7 +11654,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11656,7 +11666,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>107</v>
@@ -11677,7 +11687,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11686,13 +11696,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>200</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11710,22 +11720,22 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11758,7 +11768,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11770,7 +11780,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>197</v>
@@ -11778,7 +11788,7 @@
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -11793,7 +11803,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11805,15 +11815,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -11828,7 +11838,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11861,7 +11871,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11894,7 +11904,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11927,7 +11937,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -11939,7 +11949,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>64</v>
@@ -11960,7 +11970,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -11975,7 +11985,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11993,7 +12003,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12041,13 +12051,13 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>17</v>
@@ -12060,7 +12070,9 @@
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
-      <c r="M345" s="7"/>
+      <c t="s" r="M345" s="7">
+        <v>370</v>
+      </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
       <c t="s" r="A346" s="6">
@@ -12074,7 +12086,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12107,7 +12119,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12155,7 +12167,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12170,12 +12182,12 @@
         <v>149</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12190,7 +12202,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12202,7 +12214,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>182</v>
@@ -12223,7 +12235,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12256,7 +12268,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12271,7 +12283,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12289,7 +12301,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12298,13 +12310,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12322,22 +12334,22 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12370,7 +12382,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12379,10 +12391,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>46</v>
@@ -12403,13 +12415,13 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>17</v>
@@ -12418,7 +12430,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12436,7 +12448,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12448,7 +12460,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>145</v>
@@ -12484,7 +12496,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12499,7 +12511,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12517,7 +12529,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12550,7 +12562,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12562,7 +12574,7 @@
         <v>101</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>184</v>
@@ -12598,7 +12610,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12610,7 +12622,7 @@
         <v>101</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>79</v>
@@ -12618,7 +12630,7 @@
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -12633,7 +12645,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12666,7 +12678,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12681,7 +12693,7 @@
         <v>154</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12699,7 +12711,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12711,7 +12723,7 @@
         <v>132</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>156</v>
@@ -12732,7 +12744,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12765,7 +12777,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12798,7 +12810,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12813,7 +12825,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12846,7 +12858,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -12855,10 +12867,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>68</v>
@@ -12866,7 +12878,7 @@
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -12881,13 +12893,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>30</v>
@@ -12901,7 +12913,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -12916,7 +12928,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -12949,7 +12961,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12982,7 +12994,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -12991,7 +13003,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c t="s" r="I376" s="7">
         <v>54</v>
@@ -13015,13 +13027,13 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>30</v>
@@ -13030,7 +13042,7 @@
         <v>220</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13048,7 +13060,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13057,10 +13069,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>107</v>
@@ -13081,13 +13093,13 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>30</v>
@@ -13096,7 +13108,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13129,7 +13141,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13162,7 +13174,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13195,7 +13207,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13204,10 +13216,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>28</v>
@@ -13243,7 +13255,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13255,7 +13267,7 @@
         <v>205</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>152</v>
@@ -13263,7 +13275,7 @@
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -13278,7 +13290,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13311,7 +13323,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13320,7 +13332,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>207</v>
@@ -13344,13 +13356,13 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>30</v>
@@ -13377,7 +13389,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13410,7 +13422,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13422,10 +13434,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13458,7 +13470,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F392" s="7">
         <v>330</v>
@@ -13470,7 +13482,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>78</v>
@@ -13478,7 +13490,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -13486,14 +13498,14 @@
         <v>13</v>
       </c>
       <c r="B393" s="7">
-        <v>609</v>
+        <v>5805</v>
       </c>
       <c t="s" r="C393" s="7">
-        <v>14</v>
+        <v>211</v>
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
@@ -13502,13 +13514,13 @@
         <v>70</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>30</v>
+        <v>394</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>43</v>
+        <v>215</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13519,128 +13531,128 @@
         <v>13</v>
       </c>
       <c r="B394" s="7">
-        <v>604</v>
+        <v>2841</v>
       </c>
       <c t="s" r="C394" s="7">
-        <v>14</v>
+        <v>211</v>
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F394" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>30</v>
+        <v>394</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c r="M394" s="7"/>
     </row>
     <row r="395" ht="15" customHeight="1">
-      <c t="s" r="A395" s="6">
-        <v>13</v>
-      </c>
-      <c r="B395" s="7">
-        <v>5060</v>
-      </c>
-      <c t="s" r="C395" s="7">
-        <v>14</v>
-      </c>
+      <c r="A395" s="6"/>
+      <c r="B395" s="7"/>
+      <c r="C395" s="7"/>
       <c r="D395" s="7"/>
-      <c t="s" r="E395" s="7">
-        <v>390</v>
-      </c>
-      <c r="F395" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G395" s="8">
-        <v>70</v>
-      </c>
-      <c t="s" r="H395" s="8">
-        <v>392</v>
-      </c>
-      <c t="s" r="I395" s="7">
-        <v>112</v>
-      </c>
-      <c t="s" r="J395" s="7">
-        <v>253</v>
-      </c>
+      <c r="E395" s="7"/>
+      <c r="F395" s="7"/>
+      <c r="G395" s="8"/>
+      <c r="H395" s="8"/>
+      <c r="I395" s="7"/>
+      <c r="J395" s="7"/>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c r="M395" s="7"/>
     </row>
     <row r="396" ht="14.25" customHeight="1">
-      <c r="A396" s="6"/>
-      <c r="B396" s="7"/>
-      <c r="C396" s="7"/>
+      <c t="s" r="A396" s="6">
+        <v>13</v>
+      </c>
+      <c r="B396" s="7">
+        <v>86</v>
+      </c>
+      <c t="s" r="C396" s="7">
+        <v>14</v>
+      </c>
       <c r="D396" s="7"/>
-      <c r="E396" s="7"/>
-      <c r="F396" s="7"/>
-      <c r="G396" s="8"/>
-      <c r="H396" s="8"/>
-      <c r="I396" s="7"/>
-      <c r="J396" s="7"/>
+      <c t="s" r="E396" s="7">
+        <v>395</v>
+      </c>
+      <c r="F396" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G396" s="8">
+        <v>396</v>
+      </c>
+      <c t="s" r="H396" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I396" s="7">
+        <v>276</v>
+      </c>
+      <c t="s" r="J396" s="7">
+        <v>324</v>
+      </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
-      <c r="M396" s="7"/>
+      <c t="s" r="M396" s="7">
+        <v>397</v>
+      </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
-      <c t="s" r="A397" s="6">
-        <v>13</v>
-      </c>
-      <c r="B397" s="7">
-        <v>86</v>
-      </c>
-      <c t="s" r="C397" s="7">
-        <v>14</v>
-      </c>
+      <c r="A397" s="6"/>
+      <c r="B397" s="7"/>
+      <c r="C397" s="7"/>
       <c r="D397" s="7"/>
-      <c t="s" r="E397" s="7">
-        <v>393</v>
-      </c>
-      <c r="F397" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G397" s="8">
-        <v>394</v>
-      </c>
-      <c t="s" r="H397" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I397" s="7">
-        <v>275</v>
-      </c>
-      <c t="s" r="J397" s="7">
-        <v>323</v>
-      </c>
+      <c r="E397" s="7"/>
+      <c r="F397" s="7"/>
+      <c r="G397" s="8"/>
+      <c r="H397" s="8"/>
+      <c r="I397" s="7"/>
+      <c r="J397" s="7"/>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
-      <c t="s" r="M397" s="7">
-        <v>395</v>
-      </c>
+      <c r="M397" s="7"/>
     </row>
     <row r="398" ht="14.25" customHeight="1">
-      <c r="A398" s="6"/>
-      <c r="B398" s="7"/>
-      <c r="C398" s="7"/>
+      <c t="s" r="A398" s="6">
+        <v>13</v>
+      </c>
+      <c r="B398" s="7">
+        <v>83</v>
+      </c>
+      <c t="s" r="C398" s="7">
+        <v>14</v>
+      </c>
       <c r="D398" s="7"/>
-      <c r="E398" s="7"/>
-      <c r="F398" s="7"/>
-      <c r="G398" s="8"/>
-      <c r="H398" s="8"/>
-      <c r="I398" s="7"/>
-      <c r="J398" s="7"/>
+      <c t="s" r="E398" s="7">
+        <v>398</v>
+      </c>
+      <c r="F398" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G398" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H398" s="8">
+        <v>399</v>
+      </c>
+      <c t="s" r="I398" s="7">
+        <v>153</v>
+      </c>
+      <c t="s" r="J398" s="7">
+        <v>273</v>
+      </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c r="M398" s="7"/>
@@ -13650,78 +13662,78 @@
         <v>13</v>
       </c>
       <c r="B399" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="C399" s="7">
         <v>14</v>
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>30</v>
+        <v>399</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>397</v>
+        <v>30</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>153</v>
+        <v>400</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>272</v>
+        <v>187</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c r="M399" s="7"/>
     </row>
     <row r="400" ht="15" customHeight="1">
-      <c t="s" r="A400" s="6">
-        <v>13</v>
-      </c>
-      <c r="B400" s="7">
-        <v>84</v>
-      </c>
-      <c t="s" r="C400" s="7">
-        <v>14</v>
-      </c>
+      <c r="A400" s="6"/>
+      <c r="B400" s="7"/>
+      <c r="C400" s="7"/>
       <c r="D400" s="7"/>
-      <c t="s" r="E400" s="7">
-        <v>396</v>
-      </c>
-      <c r="F400" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G400" s="8">
-        <v>397</v>
-      </c>
-      <c t="s" r="H400" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I400" s="7">
-        <v>398</v>
-      </c>
-      <c t="s" r="J400" s="7">
-        <v>187</v>
-      </c>
+      <c r="E400" s="7"/>
+      <c r="F400" s="7"/>
+      <c r="G400" s="8"/>
+      <c r="H400" s="8"/>
+      <c r="I400" s="7"/>
+      <c r="J400" s="7"/>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c r="M400" s="7"/>
     </row>
     <row r="401" ht="14.25" customHeight="1">
-      <c r="A401" s="6"/>
-      <c r="B401" s="7"/>
-      <c r="C401" s="7"/>
+      <c t="s" r="A401" s="6">
+        <v>13</v>
+      </c>
+      <c r="B401" s="7">
+        <v>609</v>
+      </c>
+      <c t="s" r="C401" s="7">
+        <v>14</v>
+      </c>
       <c r="D401" s="7"/>
-      <c r="E401" s="7"/>
-      <c r="F401" s="7"/>
-      <c r="G401" s="8"/>
-      <c r="H401" s="8"/>
-      <c r="I401" s="7"/>
-      <c r="J401" s="7"/>
+      <c t="s" r="E401" s="7">
+        <v>401</v>
+      </c>
+      <c r="F401" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G401" s="8">
+        <v>70</v>
+      </c>
+      <c t="s" r="H401" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I401" s="7">
+        <v>43</v>
+      </c>
+      <c t="s" r="J401" s="7">
+        <v>134</v>
+      </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c r="M401" s="7"/>
@@ -13731,66 +13743,62 @@
         <v>13</v>
       </c>
       <c r="B402" s="7">
-        <v>2872</v>
+        <v>604</v>
       </c>
       <c t="s" r="C402" s="7">
         <v>14</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H402" s="8">
         <v>70</v>
       </c>
-      <c t="s" r="H402" s="8">
-        <v>400</v>
-      </c>
       <c t="s" r="I402" s="7">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>221</v>
-      </c>
-      <c t="s" r="K402" s="7">
-        <v>81</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="K402" s="7"/>
       <c r="L402" s="7"/>
-      <c t="s" r="M402" s="7">
-        <v>250</v>
-      </c>
+      <c r="M402" s="7"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
       <c t="s" r="A403" s="6">
         <v>13</v>
       </c>
       <c r="B403" s="7">
-        <v>2873</v>
+        <v>5060</v>
       </c>
       <c t="s" r="C403" s="7">
         <v>14</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>70</v>
+        <v>402</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>401</v>
+        <v>254</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13816,14 +13824,14 @@
         <v>13</v>
       </c>
       <c r="B405" s="7">
-        <v>5805</v>
+        <v>2872</v>
       </c>
       <c t="s" r="C405" s="7">
-        <v>211</v>
+        <v>14</v>
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -13832,46 +13840,50 @@
         <v>70</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>215</v>
+        <v>28</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>89</v>
-      </c>
-      <c r="K405" s="7"/>
+        <v>221</v>
+      </c>
+      <c t="s" r="K405" s="7">
+        <v>81</v>
+      </c>
       <c r="L405" s="7"/>
-      <c r="M405" s="7"/>
+      <c t="s" r="M405" s="7">
+        <v>251</v>
+      </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
       <c t="s" r="A406" s="6">
         <v>13</v>
       </c>
       <c r="B406" s="7">
-        <v>2841</v>
+        <v>2873</v>
       </c>
       <c t="s" r="C406" s="7">
-        <v>211</v>
+        <v>14</v>
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>176</v>
+        <v>405</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13904,7 +13916,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -13913,7 +13925,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>44</v>
@@ -13937,19 +13949,19 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>116</v>
@@ -13960,7 +13972,7 @@
     </row>
     <row r="410" ht="16.5" customHeight="1">
       <c t="s" r="A410" s="9">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B410" s="9"/>
       <c r="C410" s="9"/>
@@ -13980,7 +13992,7 @@
     <row r="411" ht="65.25" customHeight="1"/>
     <row r="412" ht="16.5" customHeight="1">
       <c t="s" r="A412" s="10">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B412" s="10"/>
       <c r="C412" s="10"/>
@@ -13993,7 +14005,7 @@
       <c r="J412" s="10"/>
       <c r="K412" s="10"/>
       <c t="s" r="L412" s="11">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M412" s="11"/>
       <c r="N412" s="11"/>

--- a/Data/FlightPlan/FPL_19OCT26.xlsx
+++ b/Data/FlightPlan/FPL_19OCT26.xlsx
@@ -233,6 +233,9 @@
     <t>13:35</t>
   </si>
   <si>
+    <t>13:25</t>
+  </si>
+  <si>
     <t>CZX</t>
   </si>
   <si>
@@ -305,6 +308,9 @@
     <t>VN-A529</t>
   </si>
   <si>
+    <t>13:24</t>
+  </si>
+  <si>
     <t>15:35</t>
   </si>
   <si>
@@ -329,6 +335,9 @@
     <t>12:00</t>
   </si>
   <si>
+    <t>12:08</t>
+  </si>
+  <si>
     <t>12:30</t>
   </si>
   <si>
@@ -434,6 +443,9 @@
     <t>09:10</t>
   </si>
   <si>
+    <t>11:50</t>
+  </si>
+  <si>
     <t>13:10</t>
   </si>
   <si>
@@ -575,9 +587,6 @@
     <t>10:40</t>
   </si>
   <si>
-    <t>10:43</t>
-  </si>
-  <si>
     <t>11:20</t>
   </si>
   <si>
@@ -683,9 +692,6 @@
     <t>10:05</t>
   </si>
   <si>
-    <t>11:50</t>
-  </si>
-  <si>
     <t>11:05</t>
   </si>
   <si>
@@ -713,6 +719,12 @@
     <t>09:09</t>
   </si>
   <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
     <t>16:00</t>
   </si>
   <si>
@@ -761,6 +773,9 @@
     <t>VN-A607</t>
   </si>
   <si>
+    <t>10:39</t>
+  </si>
+  <si>
     <t>MFM</t>
   </si>
   <si>
@@ -815,75 +830,78 @@
     <t>09:55</t>
   </si>
   <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
     <t>10:25</t>
   </si>
   <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
     <t>VTE</t>
   </si>
   <si>
@@ -905,6 +923,9 @@
     <t>12:35</t>
   </si>
   <si>
+    <t>12:54</t>
+  </si>
+  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -923,6 +944,9 @@
     <t>08:57</t>
   </si>
   <si>
+    <t>11:23</t>
+  </si>
+  <si>
     <t>VN-A644</t>
   </si>
   <si>
@@ -965,6 +989,9 @@
     <t>10:35</t>
   </si>
   <si>
+    <t>16:27</t>
+  </si>
+  <si>
     <t>VN-A647</t>
   </si>
   <si>
@@ -989,183 +1016,180 @@
     <t>VN-A649</t>
   </si>
   <si>
-    <t>14:14</t>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:22</t>
+  </si>
+  <si>
+    <t>09:16</t>
+  </si>
+  <si>
+    <t>11:11</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>14:13</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:32</t>
+  </si>
+  <si>
+    <t>10:42</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>11:49</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:51</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>10:44</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>10:18</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>08:28</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:42</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>12:36</t>
   </si>
   <si>
     <t>KHH</t>
   </si>
   <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:22</t>
-  </si>
-  <si>
-    <t>09:16</t>
-  </si>
-  <si>
-    <t>10:29</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>14:13</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:32</t>
-  </si>
-  <si>
-    <t>10:42</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:51</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>10:44</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>10:18</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>08:28</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:42</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>10:17</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>12:36</t>
-  </si>
-  <si>
     <t>VN-A683</t>
   </si>
   <si>
@@ -1202,7 +1226,7 @@
     <t>11:00</t>
   </si>
   <si>
-    <t>11:27</t>
+    <t>11:32</t>
   </si>
   <si>
     <t>VN-A687</t>
@@ -1229,15 +1253,15 @@
     <t>06:39</t>
   </si>
   <si>
-    <t>10:16</t>
-  </si>
-  <si>
     <t>20:15</t>
   </si>
   <si>
     <t>VN-A697</t>
   </si>
   <si>
+    <t>16:29</t>
+  </si>
+  <si>
     <t>VN-A698</t>
   </si>
   <si>
@@ -1289,6 +1313,9 @@
     <t>UFA</t>
   </si>
   <si>
+    <t>17:36</t>
+  </si>
+  <si>
     <t>05:15</t>
   </si>
   <si>
@@ -1301,7 +1328,7 @@
     <t>Total Record(s): 336</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 19, 2026 09:32</t>
+    <t xml:space="preserve">Generated on  Oct 19, 2026 10:10</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2591,7 +2618,9 @@
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
+      <c t="s" r="M31" s="7">
+        <v>74</v>
+      </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c t="s" r="A32" s="6">
@@ -2614,10 +2643,10 @@
         <v>71</v>
       </c>
       <c t="s" r="H32" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J32" s="7">
         <v>24</v>
@@ -2644,13 +2673,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G33" s="8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="H33" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J33" s="7">
         <v>68</v>
@@ -2686,7 +2715,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2695,18 +2724,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H35" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c t="s" r="M35" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
@@ -2721,13 +2750,13 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G36" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H36" s="8">
         <v>30</v>
@@ -2736,12 +2765,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c t="s" r="M36" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
@@ -2756,7 +2785,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -2765,13 +2794,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2789,22 +2818,22 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G38" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="H38" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2822,7 +2851,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -2831,13 +2860,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H39" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2855,22 +2884,22 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G40" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H40" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2888,7 +2917,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -2897,13 +2926,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H41" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I41" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2921,22 +2950,22 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H42" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2969,7 +2998,7 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -2989,7 +3018,7 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c t="s" r="M44" s="7">
-        <v>75</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -3004,7 +3033,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3019,7 +3048,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3037,7 +3066,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3046,13 +3075,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -3085,7 +3114,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3094,17 +3123,19 @@
         <v>30</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
+      <c t="s" r="M48" s="7">
+        <v>108</v>
+      </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c t="s" r="A49" s="6">
@@ -3118,19 +3149,19 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c t="s" r="J49" s="7">
         <v>33</v>
@@ -3151,7 +3182,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3163,10 +3194,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3199,22 +3230,22 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G52" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="H52" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3232,7 +3263,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3244,10 +3275,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3265,7 +3296,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3274,13 +3305,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c t="s" r="I54" s="7">
         <v>66</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3298,22 +3329,22 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3346,7 +3377,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3358,15 +3389,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c t="s" r="M57" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
@@ -3381,7 +3412,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3393,7 +3424,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J58" s="7">
         <v>72</v>
@@ -3401,7 +3432,7 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -3416,7 +3447,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3431,7 +3462,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3449,7 +3480,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3461,10 +3492,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3482,7 +3513,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3494,7 +3525,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J61" s="7">
         <v>25</v>
@@ -3515,7 +3546,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3527,7 +3558,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c t="s" r="J62" s="7">
         <v>38</v>
@@ -3563,7 +3594,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3575,7 +3606,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J64" s="7">
         <v>73</v>
@@ -3583,7 +3614,7 @@
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -3598,7 +3629,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3610,10 +3641,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3631,7 +3662,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3640,13 +3671,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3664,22 +3695,22 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3712,7 +3743,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3721,18 +3752,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -3747,13 +3778,13 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>17</v>
@@ -3762,11 +3793,13 @@
         <v>18</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
+      <c t="s" r="M70" s="7">
+        <v>144</v>
+      </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c t="s" r="A71" s="6">
@@ -3780,7 +3813,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3792,10 +3825,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3813,7 +3846,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3825,10 +3858,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3846,7 +3879,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3855,13 +3888,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3879,19 +3912,19 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c t="s" r="J74" s="7">
         <v>25</v>
@@ -3927,7 +3960,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3936,13 +3969,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3960,22 +3993,22 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3993,7 +4026,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4002,13 +4035,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4026,13 +4059,13 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>30</v>
@@ -4041,7 +4074,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4074,7 +4107,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4083,13 +4116,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H81" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4109,27 +4142,27 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G82" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="H82" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4144,7 +4177,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4153,18 +4186,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4179,22 +4212,22 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="H84" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4212,7 +4245,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4224,10 +4257,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4245,7 +4278,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4257,10 +4290,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4278,7 +4311,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4287,13 +4320,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4311,22 +4344,22 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4359,22 +4392,22 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4392,7 +4425,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4401,13 +4434,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I91" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4425,22 +4458,22 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4458,7 +4491,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4467,13 +4500,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4491,22 +4524,22 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4524,7 +4557,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4536,10 +4569,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4557,7 +4590,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4569,10 +4602,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4605,7 +4638,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4614,18 +4647,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -4633,36 +4666,36 @@
         <v>13</v>
       </c>
       <c t="s" r="B99" s="7">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c t="s" r="C99" s="7">
         <v>14</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c t="s" r="K99" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -4677,7 +4710,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4689,10 +4722,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4710,7 +4743,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4725,7 +4758,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4743,7 +4776,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4755,7 +4788,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>36</v>
@@ -4776,7 +4809,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4788,10 +4821,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4824,7 +4857,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4836,15 +4869,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -4859,7 +4892,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4871,15 +4904,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -4894,7 +4927,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4906,7 +4939,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>61</v>
@@ -4927,7 +4960,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4942,7 +4975,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4960,7 +4993,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4969,13 +5002,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4993,13 +5026,13 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>17</v>
@@ -5008,7 +5041,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5041,27 +5074,27 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5076,7 +5109,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5091,12 +5124,12 @@
         <v>50</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5111,7 +5144,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5120,13 +5153,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="I114" s="7">
         <v>61</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5144,19 +5177,19 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>27</v>
@@ -5177,7 +5210,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5186,13 +5219,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5225,7 +5258,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5234,18 +5267,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="I118" s="7">
         <v>69</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5260,19 +5293,19 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>18</v>
@@ -5280,7 +5313,7 @@
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5295,7 +5328,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5304,13 +5337,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5328,13 +5361,13 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>30</v>
@@ -5343,7 +5376,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5361,7 +5394,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5370,13 +5403,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5394,22 +5427,22 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5438,33 +5471,33 @@
         <v>7615</v>
       </c>
       <c t="s" r="C125" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="K125" s="7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -5475,11 +5508,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C126" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5491,17 +5524,17 @@
         <v>71</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>224</v>
+        <v>144</v>
       </c>
       <c t="s" r="K126" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5516,7 +5549,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5525,20 +5558,20 @@
         <v>71</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="K127" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -5553,29 +5586,29 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="K128" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5590,7 +5623,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5602,10 +5635,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5638,7 +5671,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5647,18 +5680,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -5673,13 +5706,13 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>17</v>
@@ -5688,11 +5721,13 @@
         <v>60</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
+      <c t="s" r="M132" s="7">
+        <v>227</v>
+      </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c t="s" r="A133" s="6">
@@ -5706,7 +5741,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5715,17 +5750,21 @@
         <v>17</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I133" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>106</v>
-      </c>
-      <c r="K133" s="7"/>
+        <v>109</v>
+      </c>
+      <c t="s" r="K133" s="7">
+        <v>236</v>
+      </c>
       <c r="L133" s="7"/>
-      <c r="M133" s="7"/>
+      <c t="s" r="M133" s="7">
+        <v>46</v>
+      </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
       <c t="s" r="A134" s="6">
@@ -5739,13 +5778,13 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>17</v>
@@ -5754,11 +5793,15 @@
         <v>20</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>130</v>
-      </c>
-      <c r="K134" s="7"/>
+        <v>133</v>
+      </c>
+      <c t="s" r="K134" s="7">
+        <v>237</v>
+      </c>
       <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
+      <c t="s" r="M134" s="7">
+        <v>203</v>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c t="s" r="A135" s="6">
@@ -5772,7 +5815,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5784,10 +5827,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5820,7 +5863,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5832,7 +5875,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>18</v>
@@ -5840,7 +5883,7 @@
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -5855,7 +5898,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5867,10 +5910,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5888,7 +5931,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5900,10 +5943,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5921,7 +5964,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5930,13 +5973,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5954,19 +5997,19 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>36</v>
@@ -5987,7 +6030,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5999,10 +6042,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6035,7 +6078,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6044,18 +6087,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I144" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6070,22 +6113,22 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6103,7 +6146,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6112,13 +6155,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6136,22 +6179,22 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6169,7 +6212,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6178,13 +6221,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6202,22 +6245,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6250,7 +6293,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6259,17 +6302,19 @@
         <v>30</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
-      <c r="M151" s="7"/>
+      <c t="s" r="M151" s="7">
+        <v>254</v>
+      </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
       <c t="s" r="A152" s="6">
@@ -6283,22 +6328,22 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6316,22 +6361,22 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6364,7 +6409,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6376,15 +6421,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6399,7 +6444,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6408,7 +6453,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>44</v>
@@ -6417,7 +6462,7 @@
         <v>46</v>
       </c>
       <c t="s" r="K156" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
@@ -6436,13 +6481,13 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>17</v>
@@ -6451,7 +6496,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6469,7 +6514,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6484,7 +6529,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6502,7 +6547,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6517,7 +6562,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6535,7 +6580,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6547,10 +6592,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6583,27 +6628,27 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6618,22 +6663,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6651,19 +6696,19 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>24</v>
@@ -6684,7 +6729,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6693,13 +6738,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6717,22 +6762,22 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6765,7 +6810,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6780,12 +6825,12 @@
         <v>39</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -6800,7 +6845,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6812,15 +6857,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>268</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -6835,7 +6880,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6847,10 +6892,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6868,7 +6913,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6880,10 +6925,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6901,7 +6946,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6913,7 +6958,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>56</v>
@@ -6934,7 +6979,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6943,10 +6988,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>65</v>
@@ -6967,22 +7012,22 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -7000,7 +7045,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7009,13 +7054,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7033,22 +7078,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7081,7 +7126,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7090,17 +7135,19 @@
         <v>30</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
-      <c r="M178" s="7"/>
+      <c t="s" r="M178" s="7">
+        <v>280</v>
+      </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c t="s" r="A179" s="6">
@@ -7114,22 +7161,22 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7147,7 +7194,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7156,13 +7203,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7180,19 +7227,19 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>67</v>
@@ -7228,7 +7275,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7237,18 +7284,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7263,26 +7310,28 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
-      <c r="M184" s="7"/>
+      <c t="s" r="M184" s="7">
+        <v>286</v>
+      </c>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c t="s" r="A185" s="6">
@@ -7296,7 +7345,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7308,10 +7357,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7329,7 +7378,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7341,7 +7390,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>64</v>
@@ -7362,7 +7411,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7371,13 +7420,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7395,22 +7444,22 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7443,7 +7492,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7452,18 +7501,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7478,26 +7527,28 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
-      <c r="M191" s="7"/>
+      <c t="s" r="M191" s="7">
+        <v>55</v>
+      </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c t="s" r="A192" s="6">
@@ -7511,22 +7562,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7544,22 +7595,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7577,22 +7628,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7610,22 +7661,22 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7658,7 +7709,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7667,13 +7718,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7691,13 +7742,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>30</v>
@@ -7706,7 +7757,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7724,7 +7775,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7733,13 +7784,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7757,22 +7808,22 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7805,7 +7856,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7817,15 +7868,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -7840,7 +7891,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7849,17 +7900,19 @@
         <v>30</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
-      <c r="M203" s="7"/>
+      <c t="s" r="M203" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c t="s" r="A204" s="6">
@@ -7873,13 +7926,13 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>30</v>
@@ -7888,7 +7941,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7906,7 +7959,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7915,13 +7968,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7939,22 +7992,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7987,7 +8040,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7996,10 +8049,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>72</v>
@@ -8007,7 +8060,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8022,22 +8075,22 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8055,7 +8108,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8064,13 +8117,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8088,22 +8141,22 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8136,27 +8189,27 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8171,7 +8224,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8180,17 +8233,19 @@
         <v>42</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
-      <c r="M214" s="7"/>
+      <c t="s" r="M214" s="7">
+        <v>311</v>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c t="s" r="A215" s="6">
@@ -8204,19 +8259,19 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>47</v>
@@ -8237,7 +8292,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8246,13 +8301,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8270,22 +8325,22 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8303,7 +8358,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8312,13 +8367,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8351,7 +8406,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8360,13 +8415,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8384,22 +8439,22 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8417,7 +8472,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8426,13 +8481,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8450,22 +8505,22 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8483,7 +8538,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8495,10 +8550,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8516,7 +8571,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8525,10 +8580,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>53</v>
@@ -8564,7 +8619,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8579,12 +8634,12 @@
         <v>58</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -8599,7 +8654,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8608,13 +8663,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8632,19 +8687,19 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>33</v>
@@ -8665,7 +8720,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8674,13 +8729,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8698,22 +8753,22 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8731,7 +8786,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8740,13 +8795,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8779,26 +8834,28 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
-      <c r="M234" s="7"/>
+      <c t="s" r="M234" s="7">
+        <v>326</v>
+      </c>
     </row>
     <row r="235" ht="15" customHeight="1">
       <c t="s" r="A235" s="6">
@@ -8812,7 +8869,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8860,27 +8917,27 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>319</v>
+        <v>328</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -8895,7 +8952,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8904,13 +8961,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8928,13 +8985,13 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>71</v>
@@ -8961,7 +9018,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8970,13 +9027,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9009,7 +9066,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9018,18 +9075,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9044,13 +9101,13 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>17</v>
@@ -9059,7 +9116,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9077,7 +9134,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9092,7 +9149,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9110,7 +9167,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9122,10 +9179,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9143,7 +9200,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9152,10 +9209,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>66</v>
@@ -9176,22 +9233,22 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9224,19 +9281,19 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>73</v>
@@ -9244,7 +9301,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>326</v>
+        <v>193</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9252,14 +9309,14 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>946</v>
+        <v>439</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9268,13 +9325,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>327</v>
+        <v>159</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9285,29 +9342,29 @@
         <v>13</v>
       </c>
       <c r="B251" s="7">
-        <v>947</v>
+        <v>438</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>327</v>
+        <v>159</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>217</v>
+        <v>102</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9325,7 +9382,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9334,10 +9391,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>53</v>
@@ -9373,7 +9430,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
@@ -9382,13 +9439,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9406,22 +9463,22 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9439,7 +9496,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
@@ -9448,13 +9505,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9472,22 +9529,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9505,7 +9562,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
@@ -9520,7 +9577,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9553,7 +9610,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9562,18 +9619,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9588,27 +9645,27 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -9623,7 +9680,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9632,18 +9689,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="I262" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -9658,19 +9715,19 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>61</v>
@@ -9691,7 +9748,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9700,7 +9757,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>62</v>
@@ -9724,22 +9781,22 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9757,7 +9814,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9769,10 +9826,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9790,7 +9847,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9802,10 +9859,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9838,7 +9895,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9850,7 +9907,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>54</v>
@@ -9858,7 +9915,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -9873,7 +9930,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9882,10 +9939,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>49</v>
@@ -9906,22 +9963,22 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9954,7 +10011,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9987,7 +10044,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -9999,10 +10056,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10035,7 +10092,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10044,18 +10101,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10070,27 +10127,27 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10105,27 +10162,27 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10140,13 +10197,13 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>30</v>
@@ -10173,7 +10230,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10182,13 +10239,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10206,22 +10263,22 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10239,7 +10296,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10251,10 +10308,10 @@
         <v>71</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10287,7 +10344,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10299,15 +10356,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10322,7 +10379,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10334,14 +10391,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>224</v>
+        <v>144</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
-      <c r="M285" s="7"/>
+      <c t="s" r="M285" s="7">
+        <v>356</v>
+      </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
       <c t="s" r="A286" s="6">
@@ -10355,7 +10414,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10388,7 +10447,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10400,10 +10459,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10421,7 +10480,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10433,10 +10492,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10469,7 +10528,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10478,18 +10537,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10504,26 +10563,28 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>44</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
-      <c r="M291" s="7"/>
+      <c t="s" r="M291" s="7">
+        <v>292</v>
+      </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
       <c t="s" r="A292" s="6">
@@ -10537,7 +10598,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10546,7 +10607,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I292" s="7">
         <v>22</v>
@@ -10570,13 +10631,13 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>30</v>
@@ -10585,7 +10646,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10603,7 +10664,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10612,10 +10673,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>49</v>
@@ -10636,22 +10697,22 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10684,7 +10745,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10696,15 +10757,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -10719,7 +10780,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10731,10 +10792,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10752,7 +10813,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10764,10 +10825,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10785,7 +10846,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10818,7 +10879,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10830,10 +10891,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10851,7 +10912,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -10860,10 +10921,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>18</v>
@@ -10899,7 +10960,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10911,15 +10972,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -10934,7 +10995,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10967,7 +11028,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -10976,13 +11037,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11000,22 +11061,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11048,7 +11109,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11057,18 +11118,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11083,19 +11144,19 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>46</v>
@@ -11116,7 +11177,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11125,10 +11186,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>34</v>
@@ -11149,22 +11210,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11182,7 +11243,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11191,10 +11252,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>57</v>
@@ -11215,22 +11276,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11263,7 +11324,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11275,10 +11336,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11298,7 +11359,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11310,10 +11371,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11331,7 +11392,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11340,13 +11401,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11364,22 +11425,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11397,7 +11458,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11406,13 +11467,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11430,22 +11491,22 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11478,27 +11539,27 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11513,7 +11574,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11525,13 +11586,13 @@
         <v>52</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c t="s" r="J324" s="7">
+        <v>171</v>
+      </c>
+      <c t="s" r="K324" s="7">
         <v>167</v>
-      </c>
-      <c t="s" r="K324" s="7">
-        <v>163</v>
       </c>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
@@ -11550,7 +11611,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11562,10 +11623,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11598,7 +11659,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11610,15 +11671,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -11633,7 +11694,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11645,15 +11706,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -11668,7 +11729,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11680,7 +11741,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>73</v>
@@ -11701,7 +11762,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11716,7 +11777,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11734,7 +11795,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11743,13 +11804,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11767,22 +11828,22 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11800,7 +11861,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11809,13 +11870,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11833,22 +11894,22 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11881,7 +11942,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11893,15 +11954,15 @@
         <v>71</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -11916,7 +11977,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11928,15 +11989,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>381</v>
+        <v>32</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -11951,7 +12012,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11960,17 +12021,21 @@
         <v>17</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>106</v>
-      </c>
-      <c r="K338" s="7"/>
+        <v>109</v>
+      </c>
+      <c t="s" r="K338" s="7">
+        <v>176</v>
+      </c>
       <c r="L338" s="7"/>
-      <c r="M338" s="7"/>
+      <c t="s" r="M338" s="7">
+        <v>46</v>
+      </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
       <c t="s" r="A339" s="6">
@@ -11984,13 +12049,13 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>17</v>
@@ -11999,11 +12064,15 @@
         <v>46</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>90</v>
-      </c>
-      <c r="K339" s="7"/>
+        <v>91</v>
+      </c>
+      <c t="s" r="K339" s="7">
+        <v>243</v>
+      </c>
       <c r="L339" s="7"/>
-      <c r="M339" s="7"/>
+      <c t="s" r="M339" s="7">
+        <v>127</v>
+      </c>
     </row>
     <row r="340" ht="15" customHeight="1">
       <c t="s" r="A340" s="6">
@@ -12017,7 +12086,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12026,17 +12095,21 @@
         <v>17</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>191</v>
-      </c>
-      <c r="K340" s="7"/>
+        <v>194</v>
+      </c>
+      <c t="s" r="K340" s="7">
+        <v>92</v>
+      </c>
       <c r="L340" s="7"/>
-      <c r="M340" s="7"/>
+      <c t="s" r="M340" s="7">
+        <v>281</v>
+      </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
       <c t="s" r="A341" s="6">
@@ -12050,26 +12123,30 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>65</v>
       </c>
-      <c r="K341" s="7"/>
+      <c t="s" r="K341" s="7">
+        <v>244</v>
+      </c>
       <c r="L341" s="7"/>
-      <c r="M341" s="7"/>
+      <c t="s" r="M341" s="7">
+        <v>155</v>
+      </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
       <c t="s" r="A342" s="6">
@@ -12083,7 +12160,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12092,17 +12169,21 @@
         <v>17</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>323</v>
-      </c>
-      <c r="K342" s="7"/>
+        <v>332</v>
+      </c>
+      <c t="s" r="K342" s="7">
+        <v>66</v>
+      </c>
       <c r="L342" s="7"/>
-      <c r="M342" s="7"/>
+      <c t="s" r="M342" s="7">
+        <v>314</v>
+      </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
       <c t="s" r="A343" s="6">
@@ -12116,26 +12197,30 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>37</v>
       </c>
-      <c r="K343" s="7"/>
+      <c t="s" r="K343" s="7">
+        <v>174</v>
+      </c>
       <c r="L343" s="7"/>
-      <c r="M343" s="7"/>
+      <c t="s" r="M343" s="7">
+        <v>322</v>
+      </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
       <c r="A344" s="6"/>
@@ -12164,27 +12249,27 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12192,14 +12277,14 @@
         <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>439</v>
+        <v>946</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12208,13 +12293,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>155</v>
+        <v>392</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12225,29 +12310,29 @@
         <v>13</v>
       </c>
       <c r="B347" s="7">
-        <v>438</v>
+        <v>947</v>
       </c>
       <c t="s" r="C347" s="7">
         <v>14</v>
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>155</v>
+        <v>392</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12280,27 +12365,27 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12315,22 +12400,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12348,7 +12433,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12357,13 +12442,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12381,22 +12466,22 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12414,7 +12499,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12423,13 +12508,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12447,22 +12532,22 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12495,7 +12580,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12504,10 +12589,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>46</v>
@@ -12515,7 +12600,7 @@
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -12530,13 +12615,13 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>17</v>
@@ -12545,7 +12630,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12563,7 +12648,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12572,13 +12657,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12596,22 +12681,22 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12644,7 +12729,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12653,18 +12738,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -12679,22 +12764,22 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12712,22 +12797,22 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12760,7 +12845,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12769,18 +12854,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -12795,13 +12880,13 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>30</v>
@@ -12810,12 +12895,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -12830,7 +12915,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12839,13 +12924,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12863,22 +12948,22 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12896,19 +12981,19 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>56</v>
@@ -12929,22 +13014,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12962,7 +13047,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12971,13 +13056,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13010,7 +13095,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -13019,10 +13104,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>69</v>
@@ -13030,7 +13115,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13045,19 +13130,19 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>50</v>
@@ -13065,7 +13150,7 @@
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -13080,7 +13165,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13092,7 +13177,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>32</v>
@@ -13100,7 +13185,7 @@
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>406</v>
+        <v>86</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13115,7 +13200,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13127,10 +13212,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13148,7 +13233,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13157,13 +13242,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c t="s" r="I377" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13181,22 +13266,22 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13214,7 +13299,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13223,13 +13308,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13247,22 +13332,22 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13295,7 +13380,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13315,7 +13400,7 @@
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>167</v>
+        <v>416</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -13330,7 +13415,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13342,14 +13427,18 @@
         <v>17</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>66</v>
       </c>
-      <c r="K383" s="7"/>
+      <c t="s" r="K383" s="7">
+        <v>147</v>
+      </c>
       <c r="L383" s="7"/>
-      <c r="M383" s="7"/>
+      <c t="s" r="M383" s="7">
+        <v>332</v>
+      </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
       <c t="s" r="A384" s="6">
@@ -13363,7 +13452,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13372,10 +13461,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>28</v>
@@ -13411,7 +13500,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13420,18 +13509,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -13446,13 +13535,13 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>30</v>
@@ -13461,12 +13550,12 @@
         <v>60</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -13481,7 +13570,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13490,13 +13579,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="I388" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13514,22 +13603,22 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13547,7 +13636,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13559,10 +13648,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13580,7 +13669,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13595,7 +13684,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13628,7 +13717,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
@@ -13640,15 +13729,15 @@
         <v>71</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -13663,7 +13752,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="F394" s="7">
         <v>330</v>
@@ -13672,13 +13761,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13711,27 +13800,27 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -13761,7 +13850,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
@@ -13770,13 +13859,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13794,22 +13883,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13842,7 +13931,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -13857,12 +13946,12 @@
         <v>43</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -13873,11 +13962,11 @@
         <v>20</v>
       </c>
       <c t="s" r="C402" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
@@ -13889,7 +13978,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>19</v>
@@ -13906,11 +13995,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C403" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -13919,13 +14008,13 @@
         <v>71</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="K403" s="7">
         <v>33</v>
@@ -13943,17 +14032,17 @@
         <v>2841</v>
       </c>
       <c t="s" r="C404" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>42</v>
@@ -13962,14 +14051,14 @@
         <v>23</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c t="s" r="K404" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -13999,7 +14088,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -14008,20 +14097,20 @@
         <v>71</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>28</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c t="s" r="K406" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>259</v>
+        <v>434</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14036,22 +14125,22 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>71</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14084,7 +14173,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
@@ -14093,7 +14182,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c t="s" r="I409" s="7">
         <v>44</v>
@@ -14117,22 +14206,22 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14140,7 +14229,7 @@
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c t="s" r="A411" s="9">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="B411" s="9"/>
       <c r="C411" s="9"/>
@@ -14160,7 +14249,7 @@
     <row r="412" ht="65.25" customHeight="1"/>
     <row r="413" ht="16.5" customHeight="1">
       <c t="s" r="A413" s="10">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B413" s="10"/>
       <c r="C413" s="10"/>
@@ -14173,7 +14262,7 @@
       <c r="J413" s="10"/>
       <c r="K413" s="10"/>
       <c t="s" r="L413" s="11">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="M413" s="11"/>
       <c r="N413" s="11"/>

--- a/Data/FlightPlan/FPL_19OCT26.xlsx
+++ b/Data/FlightPlan/FPL_19OCT26.xlsx
@@ -557,6 +557,9 @@
     <t>12:15</t>
   </si>
   <si>
+    <t>12:05</t>
+  </si>
+  <si>
     <t>14:20</t>
   </si>
   <si>
@@ -632,6 +635,9 @@
     <t>10:08</t>
   </si>
   <si>
+    <t>12:38</t>
+  </si>
+  <si>
     <t>15:00</t>
   </si>
   <si>
@@ -755,76 +761,376 @@
     <t>12:40</t>
   </si>
   <si>
+    <t>12:44</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>09:32</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>10:39</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>10:27</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>08:01</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>13:06</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:32</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>13:02</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:19</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>11:23</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>14:49</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>08:44</t>
+  </si>
+  <si>
+    <t>12:31</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>16:27</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>12:02</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
     <t>12:34</t>
   </si>
   <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>09:32</t>
-  </si>
-  <si>
-    <t>11:48</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>10:39</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>10:27</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>16:55</t>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:22</t>
+  </si>
+  <si>
+    <t>09:16</t>
+  </si>
+  <si>
+    <t>11:11</t>
+  </si>
+  <si>
+    <t>12:51</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>14:13</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:32</t>
+  </si>
+  <si>
+    <t>10:42</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>11:49</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:51</t>
+  </si>
+  <si>
+    <t>11:14</t>
+  </si>
+  <si>
+    <t>21:05</t>
   </si>
   <si>
     <t>MNL</t>
@@ -833,447 +1139,165 @@
     <t>22:25</t>
   </si>
   <si>
-    <t>02:10</t>
-  </si>
-  <si>
     <t>03:00</t>
   </si>
   <si>
     <t>04:35</t>
   </si>
   <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>08:01</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>11:58</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>11:18</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:06</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:32</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>13:02</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>11:19</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>11:23</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>08:44</t>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>10:44</t>
+  </si>
+  <si>
+    <t>13:32</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>10:18</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>17:26</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>08:28</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:42</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>12:36</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>10:38</t>
+  </si>
+  <si>
+    <t>13:38</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:32</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>10:09</t>
+  </si>
+  <si>
+    <t>12:01</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:39</t>
   </si>
   <si>
     <t>12:16</t>
   </si>
   <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>16:27</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>12:02</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>07:22</t>
-  </si>
-  <si>
-    <t>09:16</t>
-  </si>
-  <si>
-    <t>11:11</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>14:13</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:32</t>
-  </si>
-  <si>
-    <t>10:42</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>11:49</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:51</t>
-  </si>
-  <si>
-    <t>11:14</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>10:44</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>10:18</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>17:21</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>08:28</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:42</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>12:36</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>10:38</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:32</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>10:09</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:39</t>
-  </si>
-  <si>
     <t>20:15</t>
   </si>
   <si>
@@ -1349,10 +1373,13 @@
     <t>MEL</t>
   </si>
   <si>
+    <t>00:08</t>
+  </si>
+  <si>
     <t>Total Record(s): 334</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 19, 2026 10:53</t>
+    <t xml:space="preserve">Generated on  Oct 19, 2026 11:37</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4443,7 +4470,9 @@
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
+      <c t="s" r="M90" s="7">
+        <v>182</v>
+      </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c t="s" r="A91" s="6">
@@ -4472,7 +4501,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4532,13 +4561,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4562,16 +4591,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4601,10 +4630,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4634,10 +4663,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4670,7 +4699,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4698,14 +4727,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B99" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="C99" s="7">
         <v>14</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4717,13 +4746,13 @@
         <v>30</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J99" s="7">
+        <v>196</v>
+      </c>
+      <c t="s" r="K99" s="7">
         <v>195</v>
-      </c>
-      <c t="s" r="K99" s="7">
-        <v>194</v>
       </c>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
@@ -4742,7 +4771,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4754,10 +4783,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4775,7 +4804,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4790,7 +4819,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4808,7 +4837,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4820,7 +4849,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>37</v>
@@ -4841,7 +4870,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4853,10 +4882,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4889,7 +4918,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4901,7 +4930,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>122</v>
@@ -4909,7 +4938,7 @@
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -4924,7 +4953,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4936,15 +4965,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -4959,7 +4988,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4971,14 +5000,16 @@
         <v>43</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>62</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
+      <c t="s" r="M107" s="7">
+        <v>208</v>
+      </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c t="s" r="A108" s="6">
@@ -4992,7 +5023,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5007,7 +5038,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5025,7 +5056,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5034,7 +5065,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="I109" s="7">
         <v>154</v>
@@ -5058,13 +5089,13 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>17</v>
@@ -5091,7 +5122,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5103,10 +5134,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5139,7 +5170,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5151,15 +5182,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5174,7 +5205,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5189,12 +5220,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5209,7 +5240,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5242,7 +5273,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5254,7 +5285,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>27</v>
@@ -5275,7 +5306,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5287,10 +5318,10 @@
         <v>103</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5323,7 +5354,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5332,18 +5363,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="I119" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5358,13 +5389,13 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>30</v>
@@ -5378,7 +5409,7 @@
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5393,7 +5424,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5402,17 +5433,19 @@
         <v>30</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>170</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
-      <c r="M121" s="7"/>
+      <c t="s" r="M121" s="7">
+        <v>148</v>
+      </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c t="s" r="A122" s="6">
@@ -5426,13 +5459,13 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>30</v>
@@ -5459,7 +5492,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5468,13 +5501,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5492,22 +5525,22 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5536,26 +5569,26 @@
         <v>7615</v>
       </c>
       <c t="s" r="C126" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="K126" s="7">
         <v>160</v>
@@ -5573,11 +5606,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C127" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5589,17 +5622,17 @@
         <v>72</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>147</v>
       </c>
       <c t="s" r="K127" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -5614,7 +5647,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5632,11 +5665,11 @@
         <v>77</v>
       </c>
       <c t="s" r="K128" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5651,7 +5684,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5663,10 +5696,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="K129" s="7">
         <v>117</v>
@@ -5688,7 +5721,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5700,10 +5733,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5736,7 +5769,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5756,7 +5789,7 @@
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -5771,7 +5804,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5786,12 +5819,12 @@
         <v>61</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -5806,7 +5839,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5828,7 +5861,7 @@
       </c>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>47</v>
+        <v>90</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -5843,7 +5876,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5861,11 +5894,11 @@
         <v>136</v>
       </c>
       <c t="s" r="K135" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -5880,7 +5913,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5892,10 +5925,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5928,7 +5961,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5940,7 +5973,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>18</v>
@@ -5948,7 +5981,7 @@
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -5963,7 +5996,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5978,12 +6011,12 @@
         <v>87</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c t="s" r="M139" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
@@ -5998,7 +6031,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6010,7 +6043,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>174</v>
@@ -6031,7 +6064,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6043,7 +6076,7 @@
         <v>162</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>104</v>
@@ -6064,7 +6097,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6076,7 +6109,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>37</v>
@@ -6097,7 +6130,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6109,10 +6142,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6145,7 +6178,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6154,18 +6187,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="I145" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6180,19 +6213,19 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>171</v>
@@ -6200,7 +6233,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6215,7 +6248,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6224,10 +6257,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>154</v>
@@ -6248,13 +6281,13 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>30</v>
@@ -6263,7 +6296,7 @@
         <v>155</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6281,7 +6314,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6290,13 +6323,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6314,19 +6347,19 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>140</v>
@@ -6362,7 +6395,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6377,12 +6410,12 @@
         <v>84</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6397,7 +6430,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6406,7 +6439,7 @@
         <v>92</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="I153" s="7">
         <v>181</v>
@@ -6430,13 +6463,13 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>92</v>
@@ -6445,7 +6478,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6478,7 +6511,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6490,15 +6523,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -6513,7 +6546,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6522,7 +6555,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="I157" s="7">
         <v>45</v>
@@ -6531,11 +6564,11 @@
         <v>47</v>
       </c>
       <c t="s" r="K157" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>20</v>
+        <v>198</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6550,13 +6583,13 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>17</v>
@@ -6583,7 +6616,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6598,7 +6631,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6616,7 +6649,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6649,7 +6682,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6661,7 +6694,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>122</v>
@@ -6697,7 +6730,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6709,15 +6742,15 @@
         <v>92</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -6732,7 +6765,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6741,13 +6774,13 @@
         <v>92</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="I164" s="7">
         <v>148</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6765,13 +6798,13 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>30</v>
@@ -6791,14 +6824,14 @@
         <v>13</v>
       </c>
       <c r="B166" s="7">
-        <v>858</v>
+        <v>3900</v>
       </c>
       <c t="s" r="C166" s="7">
         <v>14</v>
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6807,13 +6840,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>274</v>
+        <v>50</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6824,20 +6857,20 @@
         <v>26</v>
       </c>
       <c r="B167" s="7">
-        <v>859</v>
+        <v>3901</v>
       </c>
       <c t="s" r="C167" s="7">
         <v>14</v>
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>30</v>
@@ -6894,7 +6927,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6969,7 +7002,7 @@
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>281</v>
+        <v>147</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -6999,11 +7032,15 @@
         <v>109</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>282</v>
-      </c>
-      <c r="K172" s="7"/>
+        <v>281</v>
+      </c>
+      <c t="s" r="K172" s="7">
+        <v>111</v>
+      </c>
       <c r="L172" s="7"/>
-      <c r="M172" s="7"/>
+      <c t="s" r="M172" s="7">
+        <v>22</v>
+      </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c t="s" r="A173" s="6">
@@ -7029,14 +7066,18 @@
         <v>30</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>57</v>
       </c>
-      <c r="K173" s="7"/>
+      <c t="s" r="K173" s="7">
+        <v>283</v>
+      </c>
       <c r="L173" s="7"/>
-      <c r="M173" s="7"/>
+      <c t="s" r="M173" s="7">
+        <v>95</v>
+      </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c t="s" r="A174" s="6">
@@ -7098,7 +7139,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7209,7 +7250,7 @@
         <v>287</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>111</v>
@@ -7244,10 +7285,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7310,7 +7351,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>68</v>
@@ -7355,7 +7396,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="I184" s="7">
         <v>122</v>
@@ -7387,7 +7428,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>17</v>
@@ -7593,10 +7634,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7629,7 +7670,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7638,7 +7679,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>122</v>
@@ -7664,19 +7705,19 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>92</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>148</v>
@@ -7684,7 +7725,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7699,7 +7740,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7708,13 +7749,13 @@
         <v>92</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7732,13 +7773,13 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>92</v>
@@ -7747,7 +7788,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7765,7 +7806,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7774,13 +7815,13 @@
         <v>92</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7798,22 +7839,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>92</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7839,14 +7880,14 @@
         <v>13</v>
       </c>
       <c r="B200" s="7">
-        <v>1813</v>
+        <v>280</v>
       </c>
       <c t="s" r="C200" s="7">
         <v>14</v>
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7855,82 +7896,62 @@
         <v>30</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>305</v>
+        <v>107</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>306</v>
+        <v>129</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
-      <c t="s" r="M200" s="7">
-        <v>74</v>
-      </c>
+      <c r="M200" s="7"/>
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c t="s" r="A201" s="6">
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>1814</v>
+        <v>281</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>305</v>
+        <v>107</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c r="M201" s="7"/>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c t="s" r="A202" s="6">
-        <v>13</v>
-      </c>
-      <c r="B202" s="7">
-        <v>1831</v>
-      </c>
-      <c t="s" r="C202" s="7">
-        <v>14</v>
-      </c>
+      <c r="A202" s="6"/>
+      <c r="B202" s="7"/>
+      <c r="C202" s="7"/>
       <c r="D202" s="7"/>
-      <c t="s" r="E202" s="7">
-        <v>304</v>
-      </c>
-      <c r="F202" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G202" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H202" s="8">
-        <v>307</v>
-      </c>
-      <c t="s" r="I202" s="7">
-        <v>175</v>
-      </c>
-      <c t="s" r="J202" s="7">
-        <v>308</v>
-      </c>
+      <c r="E202" s="7"/>
+      <c r="F202" s="7"/>
+      <c r="G202" s="8"/>
+      <c r="H202" s="8"/>
+      <c r="I202" s="7"/>
+      <c r="J202" s="7"/>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c r="M202" s="7"/>
@@ -7940,97 +7961,117 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>1832</v>
+        <v>123</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H203" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I203" s="7">
         <v>307</v>
       </c>
-      <c t="s" r="H203" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I203" s="7">
-        <v>139</v>
-      </c>
       <c t="s" r="J203" s="7">
-        <v>98</v>
+        <v>308</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
-      <c r="M203" s="7"/>
+      <c t="s" r="M203" s="7">
+        <v>309</v>
+      </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
-      <c r="A204" s="6"/>
-      <c r="B204" s="7"/>
-      <c r="C204" s="7"/>
+      <c t="s" r="A204" s="6">
+        <v>13</v>
+      </c>
+      <c r="B204" s="7">
+        <v>825</v>
+      </c>
+      <c t="s" r="C204" s="7">
+        <v>14</v>
+      </c>
       <c r="D204" s="7"/>
-      <c r="E204" s="7"/>
-      <c r="F204" s="7"/>
-      <c r="G204" s="8"/>
-      <c r="H204" s="8"/>
-      <c r="I204" s="7"/>
-      <c r="J204" s="7"/>
+      <c t="s" r="E204" s="7">
+        <v>306</v>
+      </c>
+      <c r="F204" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G204" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H204" s="8">
+        <v>310</v>
+      </c>
+      <c t="s" r="I204" s="7">
+        <v>18</v>
+      </c>
+      <c t="s" r="J204" s="7">
+        <v>311</v>
+      </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
-      <c r="M204" s="7"/>
+      <c t="s" r="M204" s="7">
+        <v>312</v>
+      </c>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c t="s" r="A205" s="6">
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>123</v>
+        <v>826</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>17</v>
+        <v>310</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>310</v>
+        <v>74</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>311</v>
+        <v>183</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
-      <c t="s" r="M205" s="7">
-        <v>312</v>
-      </c>
+      <c r="M205" s="7"/>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c t="s" r="A206" s="6">
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>825</v>
+        <v>1831</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8039,82 +8080,62 @@
         <v>30</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
-      <c t="s" r="M206" s="7">
-        <v>314</v>
-      </c>
+      <c r="M206" s="7"/>
     </row>
     <row r="207" ht="14.25" customHeight="1">
       <c t="s" r="A207" s="6">
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>826</v>
+        <v>1832</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c r="M207" s="7"/>
     </row>
     <row r="208" ht="14.25" customHeight="1">
-      <c t="s" r="A208" s="6">
-        <v>13</v>
-      </c>
-      <c r="B208" s="7">
-        <v>310</v>
-      </c>
-      <c t="s" r="C208" s="7">
-        <v>14</v>
-      </c>
+      <c r="A208" s="6"/>
+      <c r="B208" s="7"/>
+      <c r="C208" s="7"/>
       <c r="D208" s="7"/>
-      <c t="s" r="E208" s="7">
-        <v>309</v>
-      </c>
-      <c r="F208" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G208" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H208" s="8">
-        <v>86</v>
-      </c>
-      <c t="s" r="I208" s="7">
-        <v>225</v>
-      </c>
-      <c t="s" r="J208" s="7">
-        <v>104</v>
-      </c>
+      <c r="E208" s="7"/>
+      <c r="F208" s="7"/>
+      <c r="G208" s="8"/>
+      <c r="H208" s="8"/>
+      <c r="I208" s="7"/>
+      <c r="J208" s="7"/>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c r="M208" s="7"/>
@@ -8124,45 +8145,65 @@
         <v>13</v>
       </c>
       <c r="B209" s="7">
-        <v>309</v>
+        <v>809</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>30</v>
+        <v>316</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>250</v>
+        <v>167</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>289</v>
+        <v>73</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
-      <c r="M209" s="7"/>
+      <c t="s" r="M209" s="7">
+        <v>317</v>
+      </c>
     </row>
     <row r="210" ht="15" customHeight="1">
-      <c r="A210" s="6"/>
-      <c r="B210" s="7"/>
-      <c r="C210" s="7"/>
+      <c t="s" r="A210" s="6">
+        <v>13</v>
+      </c>
+      <c r="B210" s="7">
+        <v>808</v>
+      </c>
+      <c t="s" r="C210" s="7">
+        <v>14</v>
+      </c>
       <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
-      <c r="F210" s="7"/>
-      <c r="G210" s="8"/>
-      <c r="H210" s="8"/>
-      <c r="I210" s="7"/>
-      <c r="J210" s="7"/>
+      <c t="s" r="E210" s="7">
+        <v>315</v>
+      </c>
+      <c r="F210" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G210" s="8">
+        <v>316</v>
+      </c>
+      <c t="s" r="H210" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I210" s="7">
+        <v>88</v>
+      </c>
+      <c t="s" r="J210" s="7">
+        <v>91</v>
+      </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c r="M210" s="7"/>
@@ -8172,7 +8213,7 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>809</v>
+        <v>876</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
@@ -8188,26 +8229,24 @@
         <v>30</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>167</v>
+        <v>93</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
-      <c t="s" r="M211" s="7">
-        <v>317</v>
-      </c>
+      <c r="M211" s="7"/>
     </row>
     <row r="212" ht="14.25" customHeight="1">
       <c t="s" r="A212" s="6">
         <v>13</v>
       </c>
       <c r="B212" s="7">
-        <v>808</v>
+        <v>877</v>
       </c>
       <c t="s" r="C212" s="7">
         <v>14</v>
@@ -8220,50 +8259,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>91</v>
+        <v>297</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c r="M212" s="7"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
-      <c t="s" r="A213" s="6">
-        <v>13</v>
-      </c>
-      <c r="B213" s="7">
-        <v>876</v>
-      </c>
-      <c t="s" r="C213" s="7">
-        <v>14</v>
-      </c>
+      <c r="A213" s="6"/>
+      <c r="B213" s="7"/>
+      <c r="C213" s="7"/>
       <c r="D213" s="7"/>
-      <c t="s" r="E213" s="7">
-        <v>315</v>
-      </c>
-      <c r="F213" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G213" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H213" s="8">
-        <v>318</v>
-      </c>
-      <c t="s" r="I213" s="7">
-        <v>93</v>
-      </c>
-      <c t="s" r="J213" s="7">
-        <v>226</v>
-      </c>
+      <c r="E213" s="7"/>
+      <c r="F213" s="7"/>
+      <c r="G213" s="8"/>
+      <c r="H213" s="8"/>
+      <c r="I213" s="7"/>
+      <c r="J213" s="7"/>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c r="M213" s="7"/>
@@ -8273,55 +8294,77 @@
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>877</v>
+        <v>719</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>318</v>
+        <v>92</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>297</v>
+        <v>84</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
-      <c r="M214" s="7"/>
+      <c t="s" r="M214" s="7">
+        <v>320</v>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
-      <c r="A215" s="6"/>
-      <c r="B215" s="7"/>
-      <c r="C215" s="7"/>
+      <c t="s" r="A215" s="6">
+        <v>13</v>
+      </c>
+      <c r="B215" s="7">
+        <v>718</v>
+      </c>
+      <c t="s" r="C215" s="7">
+        <v>14</v>
+      </c>
       <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
-      <c r="F215" s="7"/>
-      <c r="G215" s="8"/>
-      <c r="H215" s="8"/>
-      <c r="I215" s="7"/>
-      <c r="J215" s="7"/>
+      <c t="s" r="E215" s="7">
+        <v>319</v>
+      </c>
+      <c r="F215" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G215" s="8">
+        <v>43</v>
+      </c>
+      <c t="s" r="H215" s="8">
+        <v>92</v>
+      </c>
+      <c t="s" r="I215" s="7">
+        <v>217</v>
+      </c>
+      <c t="s" r="J215" s="7">
+        <v>197</v>
+      </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
-      <c r="M215" s="7"/>
+      <c t="s" r="M215" s="7">
+        <v>321</v>
+      </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c t="s" r="A216" s="6">
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>719</v>
+        <v>1504</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
@@ -8337,26 +8380,24 @@
         <v>92</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>164</v>
+        <v>249</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
-      <c t="s" r="M216" s="7">
-        <v>320</v>
-      </c>
+      <c r="M216" s="7"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c t="s" r="A217" s="6">
         <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>718</v>
+        <v>1505</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
@@ -8369,29 +8410,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>92</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>215</v>
+        <v>136</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>196</v>
+        <v>117</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
-      <c t="s" r="M217" s="7">
-        <v>321</v>
-      </c>
+      <c r="M217" s="7"/>
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c t="s" r="A218" s="6">
         <v>13</v>
       </c>
       <c r="B218" s="7">
-        <v>1504</v>
+        <v>715</v>
       </c>
       <c t="s" r="C218" s="7">
         <v>14</v>
@@ -8407,13 +8446,13 @@
         <v>92</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>247</v>
+        <v>94</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>48</v>
+        <v>252</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8424,7 +8463,7 @@
         <v>13</v>
       </c>
       <c r="B219" s="7">
-        <v>1505</v>
+        <v>714</v>
       </c>
       <c t="s" r="C219" s="7">
         <v>14</v>
@@ -8437,50 +8476,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>92</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c r="M219" s="7"/>
     </row>
     <row r="220" ht="15" customHeight="1">
-      <c t="s" r="A220" s="6">
-        <v>13</v>
-      </c>
-      <c r="B220" s="7">
-        <v>715</v>
-      </c>
-      <c t="s" r="C220" s="7">
-        <v>14</v>
-      </c>
+      <c r="A220" s="6"/>
+      <c r="B220" s="7"/>
+      <c r="C220" s="7"/>
       <c r="D220" s="7"/>
-      <c t="s" r="E220" s="7">
-        <v>319</v>
-      </c>
-      <c r="F220" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G220" s="8">
-        <v>92</v>
-      </c>
-      <c t="s" r="H220" s="8">
-        <v>43</v>
-      </c>
-      <c t="s" r="I220" s="7">
-        <v>94</v>
-      </c>
-      <c t="s" r="J220" s="7">
-        <v>250</v>
-      </c>
+      <c r="E220" s="7"/>
+      <c r="F220" s="7"/>
+      <c r="G220" s="8"/>
+      <c r="H220" s="8"/>
+      <c r="I220" s="7"/>
+      <c r="J220" s="7"/>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c r="M220" s="7"/>
@@ -8490,45 +8511,65 @@
         <v>13</v>
       </c>
       <c r="B221" s="7">
-        <v>714</v>
+        <v>887</v>
       </c>
       <c t="s" r="C221" s="7">
         <v>14</v>
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>226</v>
+        <v>45</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
-      <c r="M221" s="7"/>
+      <c t="s" r="M221" s="7">
+        <v>323</v>
+      </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
-      <c r="A222" s="6"/>
-      <c r="B222" s="7"/>
-      <c r="C222" s="7"/>
+      <c t="s" r="A222" s="6">
+        <v>13</v>
+      </c>
+      <c r="B222" s="7">
+        <v>882</v>
+      </c>
+      <c t="s" r="C222" s="7">
+        <v>14</v>
+      </c>
       <c r="D222" s="7"/>
-      <c r="E222" s="7"/>
-      <c r="F222" s="7"/>
-      <c r="G222" s="8"/>
-      <c r="H222" s="8"/>
-      <c r="I222" s="7"/>
-      <c r="J222" s="7"/>
+      <c t="s" r="E222" s="7">
+        <v>322</v>
+      </c>
+      <c r="F222" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G222" s="8">
+        <v>272</v>
+      </c>
+      <c t="s" r="H222" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I222" s="7">
+        <v>149</v>
+      </c>
+      <c t="s" r="J222" s="7">
+        <v>94</v>
+      </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c r="M222" s="7"/>
@@ -8538,7 +8579,7 @@
         <v>13</v>
       </c>
       <c r="B223" s="7">
-        <v>887</v>
+        <v>262</v>
       </c>
       <c t="s" r="C223" s="7">
         <v>14</v>
@@ -8554,13 +8595,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>270</v>
+        <v>324</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>45</v>
+        <v>288</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8571,7 +8612,7 @@
         <v>13</v>
       </c>
       <c r="B224" s="7">
-        <v>882</v>
+        <v>263</v>
       </c>
       <c t="s" r="C224" s="7">
         <v>14</v>
@@ -8584,16 +8625,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>270</v>
+        <v>324</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>149</v>
+        <v>296</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>94</v>
+        <v>325</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8604,7 +8645,7 @@
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>262</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
@@ -8620,13 +8661,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>323</v>
+        <v>17</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8634,10 +8675,10 @@
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c t="s" r="A226" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B226" s="7">
-        <v>263</v>
+        <v>958</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
@@ -8650,150 +8691,152 @@
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>323</v>
+        <v>17</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>30</v>
+        <v>328</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>324</v>
+        <v>54</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c r="M226" s="7"/>
     </row>
     <row r="227" ht="14.25" customHeight="1">
-      <c t="s" r="A227" s="6">
-        <v>13</v>
-      </c>
-      <c r="B227" s="7">
-        <v>1128</v>
-      </c>
-      <c t="s" r="C227" s="7">
-        <v>14</v>
-      </c>
+      <c r="A227" s="6"/>
+      <c r="B227" s="7"/>
+      <c r="C227" s="7"/>
       <c r="D227" s="7"/>
-      <c t="s" r="E227" s="7">
-        <v>322</v>
-      </c>
-      <c r="F227" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G227" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H227" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I227" s="7">
-        <v>325</v>
-      </c>
-      <c t="s" r="J227" s="7">
-        <v>326</v>
-      </c>
+      <c r="E227" s="7"/>
+      <c r="F227" s="7"/>
+      <c r="G227" s="8"/>
+      <c r="H227" s="8"/>
+      <c r="I227" s="7"/>
+      <c r="J227" s="7"/>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c r="M227" s="7"/>
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c t="s" r="A228" s="6">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B228" s="7">
-        <v>958</v>
+        <v>122</v>
       </c>
       <c t="s" r="C228" s="7">
         <v>14</v>
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H228" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H228" s="8">
-        <v>327</v>
-      </c>
       <c t="s" r="I228" s="7">
-        <v>328</v>
+        <v>59</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>54</v>
+        <v>291</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
-      <c r="M228" s="7"/>
+      <c t="s" r="M228" s="7">
+        <v>331</v>
+      </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
-      <c r="A229" s="6"/>
-      <c r="B229" s="7"/>
-      <c r="C229" s="7"/>
+      <c t="s" r="A229" s="6">
+        <v>13</v>
+      </c>
+      <c r="B229" s="7">
+        <v>1491</v>
+      </c>
+      <c t="s" r="C229" s="7">
+        <v>14</v>
+      </c>
       <c r="D229" s="7"/>
-      <c r="E229" s="7"/>
-      <c r="F229" s="7"/>
-      <c r="G229" s="8"/>
-      <c r="H229" s="8"/>
-      <c r="I229" s="7"/>
-      <c r="J229" s="7"/>
+      <c t="s" r="E229" s="7">
+        <v>330</v>
+      </c>
+      <c r="F229" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G229" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H229" s="8">
+        <v>80</v>
+      </c>
+      <c t="s" r="I229" s="7">
+        <v>87</v>
+      </c>
+      <c t="s" r="J229" s="7">
+        <v>181</v>
+      </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
-      <c r="M229" s="7"/>
+      <c t="s" r="M229" s="7">
+        <v>332</v>
+      </c>
     </row>
     <row r="230" ht="15" customHeight="1">
       <c t="s" r="A230" s="6">
         <v>13</v>
       </c>
       <c r="B230" s="7">
-        <v>122</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C230" s="7">
         <v>14</v>
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>59</v>
+        <v>226</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>291</v>
+        <v>33</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
-      <c t="s" r="M230" s="7">
-        <v>330</v>
-      </c>
+      <c r="M230" s="7"/>
     </row>
     <row r="231" ht="14.25" customHeight="1">
       <c t="s" r="A231" s="6">
         <v>13</v>
       </c>
       <c r="B231" s="7">
-        <v>1491</v>
+        <v>913</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8802,48 +8845,46 @@
         <v>17</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>87</v>
+        <v>227</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>181</v>
+        <v>118</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
-      <c t="s" r="M231" s="7">
-        <v>331</v>
-      </c>
+      <c r="M231" s="7"/>
     </row>
     <row r="232" ht="14.25" customHeight="1">
       <c t="s" r="A232" s="6">
         <v>13</v>
       </c>
       <c r="B232" s="7">
-        <v>1492</v>
+        <v>914</v>
       </c>
       <c t="s" r="C232" s="7">
         <v>14</v>
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>224</v>
+        <v>151</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>33</v>
+        <v>229</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8854,14 +8895,14 @@
         <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>913</v>
+        <v>962</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8870,47 +8911,29 @@
         <v>17</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>332</v>
+        <v>103</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>225</v>
+        <v>334</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>118</v>
+        <v>307</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c r="M233" s="7"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
-      <c t="s" r="A234" s="6">
-        <v>13</v>
-      </c>
-      <c r="B234" s="7">
-        <v>914</v>
-      </c>
-      <c t="s" r="C234" s="7">
-        <v>14</v>
-      </c>
+      <c r="A234" s="6"/>
+      <c r="B234" s="7"/>
+      <c r="C234" s="7"/>
       <c r="D234" s="7"/>
-      <c t="s" r="E234" s="7">
-        <v>329</v>
-      </c>
-      <c r="F234" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G234" s="8">
-        <v>332</v>
-      </c>
-      <c t="s" r="H234" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I234" s="7">
-        <v>151</v>
-      </c>
-      <c t="s" r="J234" s="7">
-        <v>227</v>
-      </c>
+      <c r="E234" s="7"/>
+      <c r="F234" s="7"/>
+      <c r="G234" s="8"/>
+      <c r="H234" s="8"/>
+      <c r="I234" s="7"/>
+      <c r="J234" s="7"/>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c r="M234" s="7"/>
@@ -8920,128 +8943,148 @@
         <v>13</v>
       </c>
       <c r="B235" s="7">
-        <v>962</v>
+        <v>92</v>
       </c>
       <c t="s" r="C235" s="7">
         <v>14</v>
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>17</v>
+        <v>336</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>310</v>
+        <v>155</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
-      <c r="M235" s="7"/>
+      <c t="s" r="M235" s="7">
+        <v>338</v>
+      </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
-      <c r="A236" s="6"/>
-      <c r="B236" s="7"/>
-      <c r="C236" s="7"/>
+      <c t="s" r="A236" s="6">
+        <v>13</v>
+      </c>
+      <c r="B236" s="7">
+        <v>822</v>
+      </c>
+      <c t="s" r="C236" s="7">
+        <v>14</v>
+      </c>
       <c r="D236" s="7"/>
-      <c r="E236" s="7"/>
-      <c r="F236" s="7"/>
-      <c r="G236" s="8"/>
-      <c r="H236" s="8"/>
-      <c r="I236" s="7"/>
-      <c r="J236" s="7"/>
+      <c t="s" r="E236" s="7">
+        <v>335</v>
+      </c>
+      <c r="F236" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G236" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H236" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I236" s="7">
+        <v>39</v>
+      </c>
+      <c t="s" r="J236" s="7">
+        <v>54</v>
+      </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c r="M236" s="7"/>
     </row>
     <row r="237" ht="14.25" customHeight="1">
-      <c t="s" r="A237" s="6">
-        <v>13</v>
-      </c>
-      <c r="B237" s="7">
-        <v>92</v>
-      </c>
-      <c t="s" r="C237" s="7">
-        <v>14</v>
-      </c>
+      <c r="A237" s="6"/>
+      <c r="B237" s="7"/>
+      <c r="C237" s="7"/>
       <c r="D237" s="7"/>
-      <c t="s" r="E237" s="7">
-        <v>334</v>
-      </c>
-      <c r="F237" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G237" s="8">
-        <v>335</v>
-      </c>
-      <c t="s" r="H237" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I237" s="7">
-        <v>336</v>
-      </c>
-      <c t="s" r="J237" s="7">
-        <v>155</v>
-      </c>
+      <c r="E237" s="7"/>
+      <c r="F237" s="7"/>
+      <c r="G237" s="8"/>
+      <c r="H237" s="8"/>
+      <c r="I237" s="7"/>
+      <c r="J237" s="7"/>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
-      <c t="s" r="M237" s="7">
-        <v>337</v>
-      </c>
+      <c r="M237" s="7"/>
     </row>
     <row r="238" ht="14.25" customHeight="1">
       <c t="s" r="A238" s="6">
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>822</v>
+        <v>835</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>54</v>
+        <v>217</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
-      <c r="M238" s="7"/>
+      <c t="s" r="M238" s="7">
+        <v>340</v>
+      </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
-      <c r="A239" s="6"/>
-      <c r="B239" s="7"/>
-      <c r="C239" s="7"/>
+      <c t="s" r="A239" s="6">
+        <v>13</v>
+      </c>
+      <c r="B239" s="7">
+        <v>5530</v>
+      </c>
+      <c t="s" r="C239" s="7">
+        <v>14</v>
+      </c>
       <c r="D239" s="7"/>
-      <c r="E239" s="7"/>
-      <c r="F239" s="7"/>
-      <c r="G239" s="8"/>
-      <c r="H239" s="8"/>
-      <c r="I239" s="7"/>
-      <c r="J239" s="7"/>
+      <c t="s" r="E239" s="7">
+        <v>339</v>
+      </c>
+      <c r="F239" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G239" s="8">
+        <v>72</v>
+      </c>
+      <c t="s" r="H239" s="8">
+        <v>264</v>
+      </c>
+      <c t="s" r="I239" s="7">
+        <v>294</v>
+      </c>
+      <c t="s" r="J239" s="7">
+        <v>341</v>
+      </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c r="M239" s="7"/>
@@ -9051,49 +9094,47 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>835</v>
+        <v>5531</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>103</v>
+        <v>264</v>
       </c>
       <c t="s" r="H240" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
-      <c t="s" r="M240" s="7">
-        <v>339</v>
-      </c>
+      <c r="M240" s="7"/>
     </row>
     <row r="241" ht="14.25" customHeight="1">
       <c t="s" r="A241" s="6">
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>5530</v>
+        <v>834</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9102,47 +9143,29 @@
         <v>72</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>262</v>
+        <v>103</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>294</v>
+        <v>159</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>340</v>
+        <v>163</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c r="M241" s="7"/>
     </row>
     <row r="242" ht="14.25" customHeight="1">
-      <c t="s" r="A242" s="6">
-        <v>13</v>
-      </c>
-      <c r="B242" s="7">
-        <v>5531</v>
-      </c>
-      <c t="s" r="C242" s="7">
-        <v>14</v>
-      </c>
+      <c r="A242" s="6"/>
+      <c r="B242" s="7"/>
+      <c r="C242" s="7"/>
       <c r="D242" s="7"/>
-      <c t="s" r="E242" s="7">
-        <v>338</v>
-      </c>
-      <c r="F242" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G242" s="8">
-        <v>262</v>
-      </c>
-      <c t="s" r="H242" s="8">
-        <v>72</v>
-      </c>
-      <c t="s" r="I242" s="7">
-        <v>23</v>
-      </c>
-      <c t="s" r="J242" s="7">
-        <v>24</v>
-      </c>
+      <c r="E242" s="7"/>
+      <c r="F242" s="7"/>
+      <c r="G242" s="8"/>
+      <c r="H242" s="8"/>
+      <c r="I242" s="7"/>
+      <c r="J242" s="7"/>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c r="M242" s="7"/>
@@ -9152,62 +9175,84 @@
         <v>13</v>
       </c>
       <c r="B243" s="7">
-        <v>834</v>
+        <v>505</v>
       </c>
       <c t="s" r="C243" s="7">
         <v>14</v>
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>159</v>
+        <v>291</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>163</v>
+        <v>343</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
-      <c r="M243" s="7"/>
+      <c t="s" r="M243" s="7">
+        <v>196</v>
+      </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c r="A244" s="6"/>
-      <c r="B244" s="7"/>
-      <c r="C244" s="7"/>
+      <c t="s" r="A244" s="6">
+        <v>13</v>
+      </c>
+      <c r="B244" s="7">
+        <v>506</v>
+      </c>
+      <c t="s" r="C244" s="7">
+        <v>14</v>
+      </c>
       <c r="D244" s="7"/>
-      <c r="E244" s="7"/>
-      <c r="F244" s="7"/>
-      <c r="G244" s="8"/>
-      <c r="H244" s="8"/>
-      <c r="I244" s="7"/>
-      <c r="J244" s="7"/>
+      <c t="s" r="E244" s="7">
+        <v>342</v>
+      </c>
+      <c r="F244" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G244" s="8">
+        <v>92</v>
+      </c>
+      <c t="s" r="H244" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I244" s="7">
+        <v>73</v>
+      </c>
+      <c t="s" r="J244" s="7">
+        <v>181</v>
+      </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
-      <c r="M244" s="7"/>
+      <c t="s" r="M244" s="7">
+        <v>344</v>
+      </c>
     </row>
     <row r="245" ht="15" customHeight="1">
       <c t="s" r="A245" s="6">
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>505</v>
+        <v>453</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9216,48 +9261,46 @@
         <v>17</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>291</v>
+        <v>47</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
-      <c t="s" r="M245" s="7">
-        <v>195</v>
-      </c>
+      <c r="M245" s="7"/>
     </row>
     <row r="246" ht="14.25" customHeight="1">
       <c t="s" r="A246" s="6">
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>506</v>
+        <v>456</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>181</v>
+        <v>104</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9268,14 +9311,14 @@
         <v>13</v>
       </c>
       <c r="B247" s="7">
-        <v>453</v>
+        <v>521</v>
       </c>
       <c t="s" r="C247" s="7">
         <v>14</v>
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9284,13 +9327,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>342</v>
+        <v>67</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9301,63 +9344,45 @@
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>456</v>
+        <v>518</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>154</v>
+        <v>345</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>104</v>
+        <v>346</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c r="M248" s="7"/>
     </row>
     <row r="249" ht="14.25" customHeight="1">
-      <c t="s" r="A249" s="6">
-        <v>13</v>
-      </c>
-      <c r="B249" s="7">
-        <v>521</v>
-      </c>
-      <c t="s" r="C249" s="7">
-        <v>14</v>
-      </c>
+      <c r="A249" s="6"/>
+      <c r="B249" s="7"/>
+      <c r="C249" s="7"/>
       <c r="D249" s="7"/>
-      <c t="s" r="E249" s="7">
-        <v>341</v>
-      </c>
-      <c r="F249" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G249" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H249" s="8">
-        <v>92</v>
-      </c>
-      <c t="s" r="I249" s="7">
-        <v>132</v>
-      </c>
-      <c t="s" r="J249" s="7">
-        <v>67</v>
-      </c>
+      <c r="E249" s="7"/>
+      <c r="F249" s="7"/>
+      <c r="G249" s="8"/>
+      <c r="H249" s="8"/>
+      <c r="I249" s="7"/>
+      <c r="J249" s="7"/>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c r="M249" s="7"/>
@@ -9367,45 +9392,65 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>518</v>
+        <v>961</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>343</v>
+        <v>235</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>344</v>
+        <v>74</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
-      <c r="M250" s="7"/>
+      <c t="s" r="M250" s="7">
+        <v>198</v>
+      </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
-      <c r="A251" s="6"/>
-      <c r="B251" s="7"/>
-      <c r="C251" s="7"/>
+      <c t="s" r="A251" s="6">
+        <v>13</v>
+      </c>
+      <c r="B251" s="7">
+        <v>439</v>
+      </c>
+      <c t="s" r="C251" s="7">
+        <v>14</v>
+      </c>
       <c r="D251" s="7"/>
-      <c r="E251" s="7"/>
-      <c r="F251" s="7"/>
-      <c r="G251" s="8"/>
-      <c r="H251" s="8"/>
-      <c r="I251" s="7"/>
-      <c r="J251" s="7"/>
+      <c t="s" r="E251" s="7">
+        <v>347</v>
+      </c>
+      <c r="F251" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G251" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H251" s="8">
+        <v>162</v>
+      </c>
+      <c t="s" r="I251" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="J251" s="7">
+        <v>150</v>
+      </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c r="M251" s="7"/>
@@ -9415,49 +9460,47 @@
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>961</v>
+        <v>438</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>103</v>
+        <v>162</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>233</v>
+        <v>104</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
-      <c t="s" r="M252" s="7">
-        <v>197</v>
-      </c>
+      <c r="M252" s="7"/>
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c t="s" r="A253" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B253" s="7">
-        <v>439</v>
+        <v>960</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9466,95 +9509,97 @@
         <v>17</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>162</v>
+        <v>103</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>154</v>
+        <v>348</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c r="M253" s="7"/>
     </row>
     <row r="254" ht="14.25" customHeight="1">
-      <c t="s" r="A254" s="6">
-        <v>13</v>
-      </c>
-      <c r="B254" s="7">
-        <v>438</v>
-      </c>
-      <c t="s" r="C254" s="7">
-        <v>14</v>
-      </c>
+      <c r="A254" s="6"/>
+      <c r="B254" s="7"/>
+      <c r="C254" s="7"/>
       <c r="D254" s="7"/>
-      <c t="s" r="E254" s="7">
-        <v>345</v>
-      </c>
-      <c r="F254" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G254" s="8">
-        <v>162</v>
-      </c>
-      <c t="s" r="H254" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I254" s="7">
-        <v>104</v>
-      </c>
-      <c t="s" r="J254" s="7">
-        <v>158</v>
-      </c>
+      <c r="E254" s="7"/>
+      <c r="F254" s="7"/>
+      <c r="G254" s="8"/>
+      <c r="H254" s="8"/>
+      <c r="I254" s="7"/>
+      <c r="J254" s="7"/>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c r="M254" s="7"/>
     </row>
     <row r="255" ht="15" customHeight="1">
       <c t="s" r="A255" s="6">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B255" s="7">
-        <v>960</v>
+        <v>403</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F255" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G255" s="8">
         <v>17</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
-      <c r="M255" s="7"/>
+      <c t="s" r="M255" s="7">
+        <v>311</v>
+      </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c r="A256" s="6"/>
-      <c r="B256" s="7"/>
-      <c r="C256" s="7"/>
+      <c t="s" r="A256" s="6">
+        <v>13</v>
+      </c>
+      <c r="B256" s="7">
+        <v>404</v>
+      </c>
+      <c t="s" r="C256" s="7">
+        <v>14</v>
+      </c>
       <c r="D256" s="7"/>
-      <c r="E256" s="7"/>
-      <c r="F256" s="7"/>
-      <c r="G256" s="8"/>
-      <c r="H256" s="8"/>
-      <c r="I256" s="7"/>
-      <c r="J256" s="7"/>
+      <c t="s" r="E256" s="7">
+        <v>349</v>
+      </c>
+      <c r="F256" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G256" s="8">
+        <v>210</v>
+      </c>
+      <c t="s" r="H256" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I256" s="7">
+        <v>226</v>
+      </c>
+      <c t="s" r="J256" s="7">
+        <v>183</v>
+      </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c r="M256" s="7"/>
@@ -9564,14 +9609,14 @@
         <v>13</v>
       </c>
       <c r="B257" s="7">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -9580,48 +9625,46 @@
         <v>17</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
-      <c t="s" r="M257" s="7">
-        <v>313</v>
-      </c>
+      <c r="M257" s="7"/>
     </row>
     <row r="258" ht="14.25" customHeight="1">
       <c t="s" r="A258" s="6">
         <v>13</v>
       </c>
       <c r="B258" s="7">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9632,14 +9675,14 @@
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>423</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F259" s="7">
         <v>320</v>
@@ -9648,47 +9691,29 @@
         <v>17</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>183</v>
+        <v>30</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>342</v>
+        <v>37</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>184</v>
+        <v>297</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c r="M259" s="7"/>
     </row>
     <row r="260" ht="15" customHeight="1">
-      <c t="s" r="A260" s="6">
-        <v>13</v>
-      </c>
-      <c r="B260" s="7">
-        <v>424</v>
-      </c>
-      <c t="s" r="C260" s="7">
-        <v>14</v>
-      </c>
+      <c r="A260" s="6"/>
+      <c r="B260" s="7"/>
+      <c r="C260" s="7"/>
       <c r="D260" s="7"/>
-      <c t="s" r="E260" s="7">
-        <v>347</v>
-      </c>
-      <c r="F260" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G260" s="8">
-        <v>183</v>
-      </c>
-      <c t="s" r="H260" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I260" s="7">
-        <v>198</v>
-      </c>
-      <c t="s" r="J260" s="7">
-        <v>132</v>
-      </c>
+      <c r="E260" s="7"/>
+      <c r="F260" s="7"/>
+      <c r="G260" s="8"/>
+      <c r="H260" s="8"/>
+      <c r="I260" s="7"/>
+      <c r="J260" s="7"/>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c r="M260" s="7"/>
@@ -9698,62 +9723,84 @@
         <v>13</v>
       </c>
       <c r="B261" s="7">
-        <v>1127</v>
+        <v>501</v>
       </c>
       <c t="s" r="C261" s="7">
         <v>14</v>
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F261" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
         <v>17</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>37</v>
+        <v>351</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
-      <c r="M261" s="7"/>
+      <c t="s" r="M261" s="7">
+        <v>352</v>
+      </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
-      <c r="A262" s="6"/>
-      <c r="B262" s="7"/>
-      <c r="C262" s="7"/>
+      <c t="s" r="A262" s="6">
+        <v>13</v>
+      </c>
+      <c r="B262" s="7">
+        <v>514</v>
+      </c>
+      <c t="s" r="C262" s="7">
+        <v>14</v>
+      </c>
       <c r="D262" s="7"/>
-      <c r="E262" s="7"/>
-      <c r="F262" s="7"/>
-      <c r="G262" s="8"/>
-      <c r="H262" s="8"/>
-      <c r="I262" s="7"/>
-      <c r="J262" s="7"/>
+      <c t="s" r="E262" s="7">
+        <v>350</v>
+      </c>
+      <c r="F262" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G262" s="8">
+        <v>92</v>
+      </c>
+      <c t="s" r="H262" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I262" s="7">
+        <v>82</v>
+      </c>
+      <c t="s" r="J262" s="7">
+        <v>167</v>
+      </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
-      <c r="M262" s="7"/>
+      <c t="s" r="M262" s="7">
+        <v>353</v>
+      </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
       <c t="s" r="A263" s="6">
         <v>13</v>
       </c>
       <c r="B263" s="7">
-        <v>501</v>
+        <v>563</v>
       </c>
       <c t="s" r="C263" s="7">
         <v>14</v>
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9762,18 +9809,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>349</v>
+        <v>61</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>268</v>
+        <v>337</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -9781,34 +9828,34 @@
         <v>13</v>
       </c>
       <c r="B264" s="7">
-        <v>514</v>
+        <v>564</v>
       </c>
       <c t="s" r="C264" s="7">
         <v>14</v>
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>167</v>
+        <v>62</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -9816,14 +9863,14 @@
         <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>563</v>
+        <v>525</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9832,48 +9879,46 @@
         <v>17</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>336</v>
+        <v>35</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
-      <c t="s" r="M265" s="7">
-        <v>352</v>
-      </c>
+      <c r="M265" s="7"/>
     </row>
     <row r="266" ht="14.25" customHeight="1">
       <c t="s" r="A266" s="6">
         <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>564</v>
+        <v>528</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>233</v>
+        <v>356</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9884,14 +9929,14 @@
         <v>13</v>
       </c>
       <c r="B267" s="7">
-        <v>525</v>
+        <v>1157</v>
       </c>
       <c t="s" r="C267" s="7">
         <v>14</v>
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9900,13 +9945,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9917,63 +9962,45 @@
         <v>13</v>
       </c>
       <c r="B268" s="7">
-        <v>528</v>
+        <v>1156</v>
       </c>
       <c t="s" r="C268" s="7">
         <v>14</v>
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>353</v>
+        <v>97</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c r="M268" s="7"/>
     </row>
     <row r="269" ht="14.25" customHeight="1">
-      <c t="s" r="A269" s="6">
-        <v>13</v>
-      </c>
-      <c r="B269" s="7">
-        <v>1157</v>
-      </c>
-      <c t="s" r="C269" s="7">
-        <v>14</v>
-      </c>
+      <c r="A269" s="6"/>
+      <c r="B269" s="7"/>
+      <c r="C269" s="7"/>
       <c r="D269" s="7"/>
-      <c t="s" r="E269" s="7">
-        <v>348</v>
-      </c>
-      <c r="F269" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G269" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H269" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I269" s="7">
-        <v>118</v>
-      </c>
-      <c t="s" r="J269" s="7">
-        <v>199</v>
-      </c>
+      <c r="E269" s="7"/>
+      <c r="F269" s="7"/>
+      <c r="G269" s="8"/>
+      <c r="H269" s="8"/>
+      <c r="I269" s="7"/>
+      <c r="J269" s="7"/>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c r="M269" s="7"/>
@@ -9983,198 +10010,220 @@
         <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>1156</v>
+        <v>823</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
-      <c r="M270" s="7"/>
+      <c t="s" r="M270" s="7">
+        <v>358</v>
+      </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
-      <c r="A271" s="6"/>
-      <c r="B271" s="7"/>
-      <c r="C271" s="7"/>
+      <c t="s" r="A271" s="6">
+        <v>13</v>
+      </c>
+      <c r="B271" s="7">
+        <v>820</v>
+      </c>
+      <c t="s" r="C271" s="7">
+        <v>14</v>
+      </c>
       <c r="D271" s="7"/>
-      <c r="E271" s="7"/>
-      <c r="F271" s="7"/>
-      <c r="G271" s="8"/>
-      <c r="H271" s="8"/>
-      <c r="I271" s="7"/>
-      <c r="J271" s="7"/>
+      <c t="s" r="E271" s="7">
+        <v>357</v>
+      </c>
+      <c r="F271" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G271" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H271" s="8">
+        <v>359</v>
+      </c>
+      <c t="s" r="I271" s="7">
+        <v>94</v>
+      </c>
+      <c t="s" r="J271" s="7">
+        <v>50</v>
+      </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c r="M271" s="7"/>
     </row>
     <row r="272" ht="14.25" customHeight="1">
       <c t="s" r="A272" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B272" s="7">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>16</v>
+        <v>359</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>145</v>
+        <v>360</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>55</v>
+        <v>361</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
-      <c t="s" r="M272" s="7">
-        <v>355</v>
-      </c>
+      <c r="M272" s="7"/>
     </row>
     <row r="273" ht="14.25" customHeight="1">
-      <c t="s" r="A273" s="6">
-        <v>13</v>
-      </c>
-      <c r="B273" s="7">
-        <v>820</v>
-      </c>
-      <c t="s" r="C273" s="7">
-        <v>14</v>
-      </c>
+      <c r="A273" s="6"/>
+      <c r="B273" s="7"/>
+      <c r="C273" s="7"/>
       <c r="D273" s="7"/>
-      <c t="s" r="E273" s="7">
-        <v>354</v>
-      </c>
-      <c r="F273" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G273" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H273" s="8">
-        <v>356</v>
-      </c>
-      <c t="s" r="I273" s="7">
-        <v>94</v>
-      </c>
-      <c t="s" r="J273" s="7">
-        <v>50</v>
-      </c>
+      <c r="E273" s="7"/>
+      <c r="F273" s="7"/>
+      <c r="G273" s="8"/>
+      <c r="H273" s="8"/>
+      <c r="I273" s="7"/>
+      <c r="J273" s="7"/>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c r="M273" s="7"/>
     </row>
     <row r="274" ht="14.25" customHeight="1">
       <c t="s" r="A274" s="6">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B274" s="7">
-        <v>821</v>
+        <v>224</v>
       </c>
       <c t="s" r="C274" s="7">
         <v>14</v>
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>356</v>
+        <v>30</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>357</v>
+        <v>203</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
-      <c r="M274" s="7"/>
+      <c t="s" r="M274" s="7">
+        <v>364</v>
+      </c>
     </row>
     <row r="275" ht="15" customHeight="1">
-      <c r="A275" s="6"/>
-      <c r="B275" s="7"/>
-      <c r="C275" s="7"/>
+      <c t="s" r="A275" s="6">
+        <v>13</v>
+      </c>
+      <c r="B275" s="7">
+        <v>741</v>
+      </c>
+      <c t="s" r="C275" s="7">
+        <v>14</v>
+      </c>
       <c r="D275" s="7"/>
-      <c r="E275" s="7"/>
-      <c r="F275" s="7"/>
-      <c r="G275" s="8"/>
-      <c r="H275" s="8"/>
-      <c r="I275" s="7"/>
-      <c r="J275" s="7"/>
+      <c t="s" r="E275" s="7">
+        <v>362</v>
+      </c>
+      <c r="F275" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G275" s="8">
+        <v>255</v>
+      </c>
+      <c t="s" r="H275" s="8">
+        <v>80</v>
+      </c>
+      <c t="s" r="I275" s="7">
+        <v>247</v>
+      </c>
+      <c t="s" r="J275" s="7">
+        <v>127</v>
+      </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
-      <c r="M275" s="7"/>
+      <c t="s" r="M275" s="7">
+        <v>127</v>
+      </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
       <c t="s" r="A276" s="6">
         <v>13</v>
       </c>
       <c r="B276" s="7">
-        <v>224</v>
+        <v>740</v>
       </c>
       <c t="s" r="C276" s="7">
         <v>14</v>
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>202</v>
+        <v>292</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>360</v>
+        <v>196</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10182,34 +10231,34 @@
         <v>13</v>
       </c>
       <c r="B277" s="7">
-        <v>741</v>
+        <v>227</v>
       </c>
       <c t="s" r="C277" s="7">
         <v>14</v>
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>245</v>
+        <v>45</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>127</v>
+        <v>250</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10217,64 +10266,62 @@
         <v>13</v>
       </c>
       <c r="B278" s="7">
-        <v>740</v>
+        <v>278</v>
       </c>
       <c t="s" r="C278" s="7">
         <v>14</v>
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>195</v>
+        <v>117</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
-      <c t="s" r="M278" s="7">
-        <v>362</v>
-      </c>
+      <c r="M278" s="7"/>
     </row>
     <row r="279" ht="14.25" customHeight="1">
       <c t="s" r="A279" s="6">
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>253</v>
+        <v>107</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>45</v>
+        <v>175</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>47</v>
+        <v>314</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10285,14 +10332,14 @@
         <v>13</v>
       </c>
       <c r="B280" s="7">
-        <v>278</v>
+        <v>1616</v>
       </c>
       <c t="s" r="C280" s="7">
         <v>14</v>
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10301,47 +10348,29 @@
         <v>30</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>294</v>
+        <v>176</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>117</v>
+        <v>229</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c r="M280" s="7"/>
     </row>
     <row r="281" ht="14.25" customHeight="1">
-      <c t="s" r="A281" s="6">
-        <v>13</v>
-      </c>
-      <c r="B281" s="7">
-        <v>279</v>
-      </c>
-      <c t="s" r="C281" s="7">
-        <v>14</v>
-      </c>
+      <c r="A281" s="6"/>
+      <c r="B281" s="7"/>
+      <c r="C281" s="7"/>
       <c r="D281" s="7"/>
-      <c t="s" r="E281" s="7">
-        <v>359</v>
-      </c>
-      <c r="F281" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G281" s="8">
-        <v>107</v>
-      </c>
-      <c t="s" r="H281" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I281" s="7">
-        <v>175</v>
-      </c>
-      <c t="s" r="J281" s="7">
-        <v>308</v>
-      </c>
+      <c r="E281" s="7"/>
+      <c r="F281" s="7"/>
+      <c r="G281" s="8"/>
+      <c r="H281" s="8"/>
+      <c r="I281" s="7"/>
+      <c r="J281" s="7"/>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c r="M281" s="7"/>
@@ -10351,62 +10380,84 @@
         <v>13</v>
       </c>
       <c r="B282" s="7">
-        <v>1616</v>
+        <v>125</v>
       </c>
       <c t="s" r="C282" s="7">
         <v>14</v>
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F282" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>176</v>
+        <v>270</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>227</v>
+        <v>146</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
-      <c r="M282" s="7"/>
+      <c t="s" r="M282" s="7">
+        <v>145</v>
+      </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
-      <c r="A283" s="6"/>
-      <c r="B283" s="7"/>
-      <c r="C283" s="7"/>
+      <c t="s" r="A283" s="6">
+        <v>13</v>
+      </c>
+      <c r="B283" s="7">
+        <v>128</v>
+      </c>
+      <c t="s" r="C283" s="7">
+        <v>14</v>
+      </c>
       <c r="D283" s="7"/>
-      <c r="E283" s="7"/>
-      <c r="F283" s="7"/>
-      <c r="G283" s="8"/>
-      <c r="H283" s="8"/>
-      <c r="I283" s="7"/>
-      <c r="J283" s="7"/>
+      <c t="s" r="E283" s="7">
+        <v>366</v>
+      </c>
+      <c r="F283" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G283" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H283" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I283" s="7">
+        <v>221</v>
+      </c>
+      <c t="s" r="J283" s="7">
+        <v>147</v>
+      </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
-      <c r="M283" s="7"/>
+      <c t="s" r="M283" s="7">
+        <v>367</v>
+      </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
       <c t="s" r="A284" s="6">
         <v>13</v>
       </c>
       <c r="B284" s="7">
-        <v>125</v>
+        <v>775</v>
       </c>
       <c t="s" r="C284" s="7">
         <v>14</v>
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10415,18 +10466,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>268</v>
+        <v>89</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>146</v>
-      </c>
-      <c r="K284" s="7"/>
+        <v>74</v>
+      </c>
+      <c t="s" r="K284" s="7">
+        <v>111</v>
+      </c>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>145</v>
+        <v>77</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10434,34 +10487,36 @@
         <v>13</v>
       </c>
       <c r="B285" s="7">
-        <v>128</v>
+        <v>772</v>
       </c>
       <c t="s" r="C285" s="7">
         <v>14</v>
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>219</v>
+        <v>63</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>147</v>
-      </c>
-      <c r="K285" s="7"/>
+        <v>117</v>
+      </c>
+      <c t="s" r="K285" s="7">
+        <v>115</v>
+      </c>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>364</v>
+        <v>185</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10469,14 +10524,14 @@
         <v>13</v>
       </c>
       <c r="B286" s="7">
-        <v>775</v>
+        <v>1511</v>
       </c>
       <c t="s" r="C286" s="7">
         <v>14</v>
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10485,20 +10540,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>89</v>
+        <v>239</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c t="s" r="K286" s="7">
-        <v>111</v>
+        <v>368</v>
       </c>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>77</v>
+        <v>240</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10506,140 +10561,136 @@
         <v>13</v>
       </c>
       <c r="B287" s="7">
-        <v>772</v>
+        <v>1518</v>
       </c>
       <c t="s" r="C287" s="7">
         <v>14</v>
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>63</v>
+        <v>314</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>117</v>
+        <v>296</v>
       </c>
       <c t="s" r="K287" s="7">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
-      <c t="s" r="A288" s="6">
-        <v>13</v>
-      </c>
-      <c r="B288" s="7">
-        <v>1511</v>
-      </c>
-      <c t="s" r="C288" s="7">
-        <v>14</v>
-      </c>
+      <c r="A288" s="6"/>
+      <c r="B288" s="7"/>
+      <c r="C288" s="7"/>
       <c r="D288" s="7"/>
-      <c t="s" r="E288" s="7">
-        <v>363</v>
-      </c>
-      <c r="F288" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G288" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H288" s="8">
-        <v>92</v>
-      </c>
-      <c t="s" r="I288" s="7">
-        <v>237</v>
-      </c>
-      <c t="s" r="J288" s="7">
-        <v>131</v>
-      </c>
-      <c t="s" r="K288" s="7">
-        <v>365</v>
-      </c>
+      <c r="E288" s="7"/>
+      <c r="F288" s="7"/>
+      <c r="G288" s="8"/>
+      <c r="H288" s="8"/>
+      <c r="I288" s="7"/>
+      <c r="J288" s="7"/>
+      <c r="K288" s="7"/>
       <c r="L288" s="7"/>
-      <c t="s" r="M288" s="7">
-        <v>238</v>
-      </c>
+      <c r="M288" s="7"/>
     </row>
     <row r="289" ht="14.25" customHeight="1">
       <c t="s" r="A289" s="6">
         <v>13</v>
       </c>
       <c r="B289" s="7">
-        <v>1518</v>
+        <v>382</v>
       </c>
       <c t="s" r="C289" s="7">
         <v>14</v>
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F289" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>17</v>
+        <v>162</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>308</v>
+        <v>370</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>296</v>
-      </c>
-      <c t="s" r="K289" s="7">
-        <v>295</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>188</v>
+        <v>371</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
-      <c r="A290" s="6"/>
-      <c r="B290" s="7"/>
-      <c r="C290" s="7"/>
+      <c t="s" r="A290" s="6">
+        <v>13</v>
+      </c>
+      <c r="B290" s="7">
+        <v>383</v>
+      </c>
+      <c t="s" r="C290" s="7">
+        <v>14</v>
+      </c>
       <c r="D290" s="7"/>
-      <c r="E290" s="7"/>
-      <c r="F290" s="7"/>
-      <c r="G290" s="8"/>
-      <c r="H290" s="8"/>
-      <c r="I290" s="7"/>
-      <c r="J290" s="7"/>
+      <c t="s" r="E290" s="7">
+        <v>369</v>
+      </c>
+      <c r="F290" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G290" s="8">
+        <v>162</v>
+      </c>
+      <c t="s" r="H290" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I290" s="7">
+        <v>234</v>
+      </c>
+      <c t="s" r="J290" s="7">
+        <v>45</v>
+      </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
-      <c r="M290" s="7"/>
+      <c t="s" r="M290" s="7">
+        <v>372</v>
+      </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
       <c t="s" r="A291" s="6">
         <v>13</v>
       </c>
       <c r="B291" s="7">
-        <v>382</v>
+        <v>1813</v>
       </c>
       <c t="s" r="C291" s="7">
         <v>14</v>
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10648,18 +10699,20 @@
         <v>30</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>162</v>
+        <v>310</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>215</v>
-      </c>
-      <c r="K291" s="7"/>
+        <v>198</v>
+      </c>
+      <c t="s" r="K291" s="7">
+        <v>90</v>
+      </c>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>368</v>
+        <v>149</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -10667,34 +10720,36 @@
         <v>13</v>
       </c>
       <c r="B292" s="7">
-        <v>383</v>
+        <v>1814</v>
       </c>
       <c t="s" r="C292" s="7">
         <v>14</v>
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>162</v>
+        <v>310</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>232</v>
+        <v>33</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>45</v>
-      </c>
-      <c r="K292" s="7"/>
+        <v>129</v>
+      </c>
+      <c t="s" r="K292" s="7">
+        <v>155</v>
+      </c>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>369</v>
+        <v>199</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -10702,14 +10757,14 @@
         <v>13</v>
       </c>
       <c r="B293" s="7">
-        <v>210</v>
+        <v>310</v>
       </c>
       <c t="s" r="C293" s="7">
         <v>14</v>
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10718,64 +10773,72 @@
         <v>30</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>253</v>
+        <v>86</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>64</v>
-      </c>
-      <c r="K293" s="7"/>
+        <v>104</v>
+      </c>
+      <c t="s" r="K293" s="7">
+        <v>23</v>
+      </c>
       <c r="L293" s="7"/>
-      <c r="M293" s="7"/>
+      <c t="s" r="M293" s="7">
+        <v>295</v>
+      </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
       <c t="s" r="A294" s="6">
         <v>13</v>
       </c>
       <c r="B294" s="7">
-        <v>211</v>
+        <v>309</v>
       </c>
       <c t="s" r="C294" s="7">
         <v>14</v>
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>253</v>
+        <v>86</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>57</v>
+        <v>252</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>258</v>
-      </c>
-      <c r="K294" s="7"/>
+        <v>289</v>
+      </c>
+      <c t="s" r="K294" s="7">
+        <v>176</v>
+      </c>
       <c r="L294" s="7"/>
-      <c r="M294" s="7"/>
+      <c t="s" r="M294" s="7">
+        <v>373</v>
+      </c>
     </row>
     <row r="295" ht="15" customHeight="1">
       <c t="s" r="A295" s="6">
         <v>13</v>
       </c>
       <c r="B295" s="7">
-        <v>3900</v>
+        <v>858</v>
       </c>
       <c t="s" r="C295" s="7">
         <v>14</v>
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10784,13 +10847,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>78</v>
+        <v>375</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>50</v>
+        <v>299</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10801,29 +10864,29 @@
         <v>26</v>
       </c>
       <c r="B296" s="7">
-        <v>3901</v>
+        <v>859</v>
       </c>
       <c t="s" r="C296" s="7">
         <v>14</v>
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10856,7 +10919,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10868,7 +10931,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>180</v>
@@ -10876,7 +10939,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -10891,7 +10954,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10903,14 +10966,16 @@
         <v>30</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
-      <c r="M299" s="7"/>
+      <c t="s" r="M299" s="7">
+        <v>381</v>
+      </c>
     </row>
     <row r="300" ht="15" customHeight="1">
       <c t="s" r="A300" s="6">
@@ -10924,7 +10989,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10936,10 +11001,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10957,7 +11022,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10990,7 +11055,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11023,7 +11088,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -11032,10 +11097,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>18</v>
@@ -11071,7 +11136,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11086,12 +11151,12 @@
         <v>82</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11106,7 +11171,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11126,7 +11191,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>248</v>
+        <v>344</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11134,14 +11199,14 @@
         <v>13</v>
       </c>
       <c r="B307" s="7">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c t="s" r="C307" s="7">
         <v>14</v>
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11150,13 +11215,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11167,29 +11232,29 @@
         <v>13</v>
       </c>
       <c r="B308" s="7">
-        <v>281</v>
+        <v>211</v>
       </c>
       <c t="s" r="C308" s="7">
         <v>14</v>
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11222,7 +11287,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11231,18 +11296,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11257,13 +11322,13 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>30</v>
@@ -11290,7 +11355,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11299,7 +11364,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="I312" s="7">
         <v>136</v>
@@ -11323,22 +11388,22 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11356,7 +11421,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11365,7 +11430,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c t="s" r="I314" s="7">
         <v>118</v>
@@ -11389,22 +11454,22 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11437,7 +11502,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11472,7 +11537,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11484,10 +11549,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11505,7 +11570,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11514,7 +11579,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="I319" s="7">
         <v>48</v>
@@ -11538,22 +11603,22 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11571,7 +11636,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11580,10 +11645,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>285</v>
@@ -11604,22 +11669,22 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11652,7 +11717,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11664,7 +11729,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>145</v>
@@ -11687,7 +11752,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11699,7 +11764,7 @@
         <v>53</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>175</v>
@@ -11709,7 +11774,7 @@
       </c>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -11724,7 +11789,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11739,7 +11804,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11772,7 +11837,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11787,12 +11852,12 @@
         <v>81</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -11807,7 +11872,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11822,7 +11887,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11857,7 +11922,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11869,15 +11934,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -11892,7 +11957,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11904,7 +11969,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>279</v>
@@ -11927,7 +11992,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11939,7 +12004,7 @@
         <v>143</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>111</v>
@@ -11949,7 +12014,7 @@
       </c>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -11964,7 +12029,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11982,7 +12047,7 @@
         <v>93</v>
       </c>
       <c t="s" r="K334" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
@@ -12001,7 +12066,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12016,7 +12081,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="K335" s="7">
         <v>94</v>
@@ -12038,7 +12103,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12056,7 +12121,7 @@
         <v>66</v>
       </c>
       <c t="s" r="K336" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
@@ -12075,7 +12140,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12090,14 +12155,14 @@
         <v>158</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="K337" s="7">
         <v>67</v>
       </c>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12112,7 +12177,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12124,7 +12189,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>38</v>
@@ -12134,7 +12199,7 @@
       </c>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12164,27 +12229,27 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12199,7 +12264,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12208,13 +12273,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c t="s" r="I341" s="7">
         <v>136</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12232,19 +12297,19 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>177</v>
@@ -12280,7 +12345,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -12300,7 +12365,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12315,7 +12380,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12330,11 +12395,13 @@
         <v>280</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
-      <c r="M345" s="7"/>
+      <c t="s" r="M345" s="7">
+        <v>408</v>
+      </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
       <c t="s" r="A346" s="6">
@@ -12348,7 +12415,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12357,13 +12424,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="I346" s="7">
         <v>173</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12381,13 +12448,13 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>30</v>
@@ -12414,7 +12481,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12426,10 +12493,10 @@
         <v>298</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12447,7 +12514,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12459,10 +12526,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12495,7 +12562,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12507,7 +12574,7 @@
         <v>287</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>47</v>
@@ -12515,7 +12582,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12530,7 +12597,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12545,7 +12612,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12563,7 +12630,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12572,13 +12639,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>370</v>
+        <v>274</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12596,22 +12663,22 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>370</v>
+        <v>274</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12644,7 +12711,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12659,12 +12726,12 @@
         <v>84</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -12679,7 +12746,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12688,7 +12755,7 @@
         <v>107</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>155</v>
@@ -12712,22 +12779,22 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>107</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12760,7 +12827,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12772,7 +12839,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>82</v>
@@ -12780,7 +12847,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -12795,7 +12862,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12815,7 +12882,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -12830,7 +12897,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12845,11 +12912,13 @@
         <v>170</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>415</v>
+        <v>182</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
-      <c r="M362" s="7"/>
+      <c t="s" r="M362" s="7">
+        <v>422</v>
+      </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
       <c t="s" r="A363" s="6">
@@ -12863,7 +12932,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12875,7 +12944,7 @@
         <v>143</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>173</v>
@@ -12896,7 +12965,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12908,7 +12977,7 @@
         <v>92</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>57</v>
@@ -12929,7 +12998,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12962,7 +13031,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -13010,7 +13079,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13019,10 +13088,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>70</v>
@@ -13030,7 +13099,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13045,13 +13114,13 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>30</v>
@@ -13065,7 +13134,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13080,7 +13149,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13115,7 +13184,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13134,7 +13203,9 @@
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
-      <c r="M371" s="7"/>
+      <c t="s" r="M371" s="7">
+        <v>428</v>
+      </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
       <c t="s" r="A372" s="6">
@@ -13148,7 +13219,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13157,7 +13228,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>55</v>
@@ -13181,22 +13252,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13214,7 +13285,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13223,10 +13294,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>296</v>
@@ -13247,22 +13318,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13295,7 +13366,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13315,7 +13386,7 @@
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13330,7 +13401,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13352,7 +13423,7 @@
       </c>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13367,7 +13438,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13376,10 +13447,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>28</v>
@@ -13415,7 +13486,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13424,10 +13495,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>167</v>
@@ -13435,7 +13506,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13450,13 +13521,13 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>30</v>
@@ -13465,12 +13536,12 @@
         <v>61</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -13485,7 +13556,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13494,13 +13565,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="I383" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13518,13 +13589,13 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>30</v>
@@ -13551,7 +13622,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13566,7 +13637,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13584,7 +13655,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13599,7 +13670,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13632,7 +13703,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="F388" s="7">
         <v>330</v>
@@ -13644,7 +13715,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>81</v>
@@ -13652,7 +13723,7 @@
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -13667,7 +13738,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="F389" s="7">
         <v>330</v>
@@ -13676,13 +13747,13 @@
         <v>72</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>139</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>275</v>
+        <v>376</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13715,27 +13786,27 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F391" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -13750,7 +13821,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F392" s="7">
         <v>330</v>
@@ -13783,7 +13854,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
@@ -13795,10 +13866,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13831,7 +13902,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="F395" s="7">
         <v>330</v>
@@ -13840,7 +13911,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c t="s" r="I395" s="7">
         <v>168</v>
@@ -13851,7 +13922,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -13866,22 +13937,22 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13914,7 +13985,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
@@ -13945,11 +14016,11 @@
         <v>20</v>
       </c>
       <c t="s" r="C399" s="7">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
@@ -13978,11 +14049,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C400" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
@@ -13991,10 +14062,10 @@
         <v>72</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>94</v>
@@ -14015,17 +14086,17 @@
         <v>2841</v>
       </c>
       <c t="s" r="C401" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>43</v>
@@ -14034,10 +14105,10 @@
         <v>23</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="K401" s="7">
-        <v>273</v>
+        <v>375</v>
       </c>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
@@ -14071,7 +14142,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -14080,7 +14151,7 @@
         <v>72</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c t="s" r="I403" s="7">
         <v>28</v>
@@ -14093,7 +14164,7 @@
       </c>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14108,13 +14179,13 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>72</v>
@@ -14123,7 +14194,7 @@
         <v>131</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -14156,7 +14227,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -14165,7 +14236,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>45</v>
@@ -14175,7 +14246,9 @@
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
-      <c r="M406" s="7"/>
+      <c t="s" r="M406" s="7">
+        <v>454</v>
+      </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
       <c t="s" r="A407" s="6">
@@ -14189,19 +14262,19 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>124</v>
@@ -14212,7 +14285,7 @@
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c t="s" r="A408" s="9">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="B408" s="9"/>
       <c r="C408" s="9"/>
@@ -14232,7 +14305,7 @@
     <row r="409" ht="65.25" customHeight="1"/>
     <row r="410" ht="17.25" customHeight="1">
       <c t="s" r="A410" s="10">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="B410" s="10"/>
       <c r="C410" s="10"/>
@@ -14245,7 +14318,7 @@
       <c r="J410" s="10"/>
       <c r="K410" s="10"/>
       <c t="s" r="L410" s="11">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="M410" s="11"/>
       <c r="N410" s="11"/>
